--- a/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_12_48.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_12_48.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4330497.983829143</v>
+        <v>4331483.190379544</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13582731.73276779</v>
+        <v>13595871.025471</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13582731.73276779</v>
+        <v>13595871.025471</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>561.0660572015665</v>
+        <v>8356.225371558976</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>561.0660572015665</v>
+        <v>8356.225371558976</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19815244.54696266</v>
+        <v>19812836.15052963</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557414</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H2" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>87.30283556964716</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -739,22 +739,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>9.350829326972439</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,19 +778,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S3" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>4.473444462796863</v>
+        <v>334.4750908757255</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N4" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O4" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,10 +906,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>5.146009903586449</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81023156784903</v>
+        <v>5.722467174369123</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -982,16 +982,16 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>283.2200026818319</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,19 +1015,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S6" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T6" t="n">
-        <v>374</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
-        <v>292.2764940197005</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O7" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,10 +1143,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>5.146009903586449</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1176,16 +1176,16 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.953406460791602</v>
       </c>
       <c r="S8" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>231.5492368695502</v>
+        <v>374</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1225,10 +1225,10 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>257.6762258465768</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,19 +1252,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>374</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S9" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T9" t="n">
-        <v>4.473444462796863</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1273,7 +1273,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>374</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N10" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O10" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P10" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1380,10 +1380,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.36239741264433</v>
+        <v>81.36239741264436</v>
       </c>
       <c r="H11" t="n">
-        <v>72.7233722713666</v>
+        <v>72.72337227136661</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9247431442083234</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>142.0601778525742</v>
@@ -1422,7 +1422,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U11" t="n">
-        <v>328.109698558661</v>
+        <v>325.1536417028693</v>
       </c>
       <c r="V11" t="n">
         <v>308.8510241668239</v>
@@ -1450,19 +1450,19 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>132.2921036807063</v>
       </c>
       <c r="E12" t="n">
-        <v>204.8313640010564</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>3.993158516536766</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H12" t="n">
-        <v>3.959653224156966</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R12" t="n">
         <v>179.932929367851</v>
@@ -1498,10 +1498,10 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T12" t="n">
-        <v>81.34934068921194</v>
+        <v>81.34934068921193</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16125598660182</v>
+        <v>79.16125598660184</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
@@ -1513,7 +1513,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9.517497010238174</v>
+        <v>9.517497010238188</v>
       </c>
       <c r="M13" t="n">
         <v>101.5443818943532</v>
@@ -1562,19 +1562,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O13" t="n">
-        <v>231.000383751146</v>
+        <v>231.0003837511461</v>
       </c>
       <c r="P13" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q13" t="n">
-        <v>352.4422664255979</v>
+        <v>352.442266425598</v>
       </c>
       <c r="R13" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S13" t="n">
-        <v>30.46857806351119</v>
+        <v>30.46857806351117</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9247431442083234</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>142.0601778525742</v>
+        <v>139.1041209967824</v>
       </c>
       <c r="T14" t="n">
         <v>259.5690792160011</v>
@@ -1687,10 +1687,10 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
         <v>339.6362423378769</v>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>179.932929367851</v>
@@ -1750,7 +1750,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>183.7458095491382</v>
+        <v>261.5506595452782</v>
       </c>
     </row>
     <row r="16">
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9247431442083234</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>142.0601778525742</v>
@@ -1902,7 +1902,7 @@
         <v>308.8510241668239</v>
       </c>
       <c r="W17" t="n">
-        <v>317.3734759809475</v>
+        <v>314.4174191251558</v>
       </c>
       <c r="X17" t="n">
         <v>271.2818334606677</v>
@@ -1921,7 +1921,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>145.4543292285231</v>
+        <v>223.2591792246631</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>179.932929367851</v>
@@ -2124,10 +2124,10 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9247431442083234</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>142.0601778525742</v>
+        <v>139.1041209967824</v>
       </c>
       <c r="T20" t="n">
         <v>259.5690792160011</v>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>179.932929367851</v>
@@ -2212,7 +2212,7 @@
         <v>81.34934068921194</v>
       </c>
       <c r="U21" t="n">
-        <v>400.1612559866018</v>
+        <v>262.3205227657455</v>
       </c>
       <c r="V21" t="n">
         <v>414.5106671915202</v>
@@ -2221,7 +2221,7 @@
         <v>432.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>204.2171562283914</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y21" t="n">
         <v>78.39139276613435</v>
@@ -2328,10 +2328,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>81.36239741264436</v>
+        <v>81.36239741264433</v>
       </c>
       <c r="H23" t="n">
-        <v>72.72337227136661</v>
+        <v>72.7233722713666</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9247431442083234</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>142.0601778525742</v>
@@ -2370,13 +2370,13 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U23" t="n">
-        <v>328.1096985586609</v>
+        <v>328.109698558661</v>
       </c>
       <c r="V23" t="n">
         <v>308.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>317.3734759809475</v>
+        <v>314.4174191251748</v>
       </c>
       <c r="X23" t="n">
         <v>271.2818334606677</v>
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63.55655664632661</v>
+        <v>246.7158234254704</v>
       </c>
       <c r="C24" t="n">
-        <v>145.4543292285231</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
@@ -2407,10 +2407,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>3.993158516536777</v>
+        <v>3.993158516536766</v>
       </c>
       <c r="H24" t="n">
-        <v>3.95965322415698</v>
+        <v>3.959653224156966</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>179.932929367851</v>
@@ -2446,10 +2446,10 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T24" t="n">
-        <v>81.34934068921193</v>
+        <v>81.34934068921194</v>
       </c>
       <c r="U24" t="n">
-        <v>79.16125598660184</v>
+        <v>79.16125598660182</v>
       </c>
       <c r="V24" t="n">
         <v>93.51066719152016</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>9.517497010238188</v>
+        <v>9.517497010238174</v>
       </c>
       <c r="M25" t="n">
         <v>101.5443818943532</v>
@@ -2510,19 +2510,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O25" t="n">
-        <v>231.0003837511461</v>
+        <v>231.000383751146</v>
       </c>
       <c r="P25" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q25" t="n">
-        <v>352.442266425598</v>
+        <v>352.4422664255979</v>
       </c>
       <c r="R25" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S25" t="n">
-        <v>30.46857806351117</v>
+        <v>30.46857806351119</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,13 +2565,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>81.36239741264436</v>
+        <v>78.40634055688666</v>
       </c>
       <c r="H26" t="n">
-        <v>72.72337227136661</v>
+        <v>72.7233722713666</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9247431442085484</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U26" t="n">
-        <v>328.1096985586609</v>
+        <v>328.109698558661</v>
       </c>
       <c r="V26" t="n">
         <v>308.8510241668239</v>
@@ -2632,22 +2632,22 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>26.93768689770263</v>
+        <v>210.096953676846</v>
       </c>
       <c r="E27" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F27" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>3.993158516536777</v>
+        <v>3.993158516536766</v>
       </c>
       <c r="H27" t="n">
-        <v>3.95965322415698</v>
+        <v>3.959653224156966</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2683,22 +2683,22 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T27" t="n">
-        <v>81.34934068921193</v>
+        <v>81.34934068921194</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16125598660184</v>
+        <v>79.16125598660182</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W27" t="n">
-        <v>294.5324096889722</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y27" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.517497010238188</v>
+        <v>9.517497010238174</v>
       </c>
       <c r="M28" t="n">
         <v>101.5443818943532</v>
@@ -2747,19 +2747,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O28" t="n">
-        <v>231.0003837511461</v>
+        <v>231.000383751146</v>
       </c>
       <c r="P28" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q28" t="n">
-        <v>352.442266425598</v>
+        <v>352.4422664255979</v>
       </c>
       <c r="R28" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S28" t="n">
-        <v>30.46857806351117</v>
+        <v>30.46857806351119</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,13 +2802,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>81.36239741264433</v>
+        <v>81.36239741264436</v>
       </c>
       <c r="H29" t="n">
-        <v>72.7233722713666</v>
+        <v>69.76731541563434</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9247431442083656</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>-2.521119313314557e-11</v>
       </c>
       <c r="S29" t="n">
         <v>142.0601778525742</v>
@@ -2844,7 +2844,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U29" t="n">
-        <v>328.109698558661</v>
+        <v>328.1096985586609</v>
       </c>
       <c r="V29" t="n">
         <v>308.8510241668239</v>
@@ -2866,25 +2866,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>40.09991244551929</v>
+        <v>223.2591792246626</v>
       </c>
       <c r="D30" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>123.9906591208808</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
-        <v>3.993158516536766</v>
+        <v>3.993158516536777</v>
       </c>
       <c r="H30" t="n">
-        <v>3.959653224156966</v>
+        <v>3.95965322415698</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>179.932929367851</v>
@@ -2920,10 +2920,10 @@
         <v>131.7003678891396</v>
       </c>
       <c r="T30" t="n">
-        <v>81.34934068921194</v>
+        <v>81.34934068921193</v>
       </c>
       <c r="U30" t="n">
-        <v>79.16125598660182</v>
+        <v>79.16125598660184</v>
       </c>
       <c r="V30" t="n">
         <v>93.51066719152016</v>
@@ -2932,7 +2932,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y30" t="n">
         <v>78.39139276613435</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9.517497010238174</v>
+        <v>9.517497010238188</v>
       </c>
       <c r="M31" t="n">
         <v>101.5443818943532</v>
@@ -2984,19 +2984,19 @@
         <v>154.4301408454554</v>
       </c>
       <c r="O31" t="n">
-        <v>231.000383751146</v>
+        <v>231.0003837511461</v>
       </c>
       <c r="P31" t="n">
         <v>290.7677661807365</v>
       </c>
       <c r="Q31" t="n">
-        <v>352.4422664255979</v>
+        <v>352.442266425598</v>
       </c>
       <c r="R31" t="n">
         <v>377.4666853582003</v>
       </c>
       <c r="S31" t="n">
-        <v>30.46857806351119</v>
+        <v>30.46857806351117</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3042,7 +3042,7 @@
         <v>81.36239741264433</v>
       </c>
       <c r="H32" t="n">
-        <v>73.64811541557496</v>
+        <v>72.7233722713666</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>259.5690792160011</v>
       </c>
       <c r="U32" t="n">
-        <v>328.109698558661</v>
+        <v>325.1536417029033</v>
       </c>
       <c r="V32" t="n">
         <v>308.8510241668239</v>
@@ -3106,7 +3106,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>145.4543292285231</v>
+        <v>223.2591792246626</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>179.932929367851</v>
@@ -3276,10 +3276,10 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>56.65754055685252</v>
+        <v>52.77674055691677</v>
       </c>
       <c r="H35" t="n">
-        <v>48.7233722713666</v>
+        <v>48.72337227136661</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.440639607608318e-11</v>
       </c>
       <c r="S35" t="n">
         <v>118.0601778525742</v>
@@ -3318,7 +3318,7 @@
         <v>235.5690792160011</v>
       </c>
       <c r="U35" t="n">
-        <v>304.109698558661</v>
+        <v>304.1096985586609</v>
       </c>
       <c r="V35" t="n">
         <v>284.8510241668239</v>
@@ -3343,16 +3343,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>361.0999124455193</v>
+        <v>16.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>2.937686897702633</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>80.74832085771396</v>
+        <v>83.94446820505107</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3394,10 +3394,10 @@
         <v>107.7003678891396</v>
       </c>
       <c r="T36" t="n">
-        <v>57.34934068921194</v>
+        <v>57.34934068921193</v>
       </c>
       <c r="U36" t="n">
-        <v>55.16125598660182</v>
+        <v>55.16125598660184</v>
       </c>
       <c r="V36" t="n">
         <v>69.51066719152016</v>
@@ -3406,7 +3406,7 @@
         <v>87.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>419.8627394453875</v>
+        <v>74.86273944538755</v>
       </c>
       <c r="Y36" t="n">
         <v>54.39139276613435</v>
@@ -3452,25 +3452,25 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>77.54438189435319</v>
+        <v>77.54438189435318</v>
       </c>
       <c r="N37" t="n">
         <v>130.4301408454554</v>
       </c>
       <c r="O37" t="n">
-        <v>207.000383751146</v>
+        <v>207.0003837511461</v>
       </c>
       <c r="P37" t="n">
         <v>266.7677661807365</v>
       </c>
       <c r="Q37" t="n">
-        <v>328.4422664255979</v>
+        <v>328.442266425598</v>
       </c>
       <c r="R37" t="n">
         <v>353.4666853582003</v>
       </c>
       <c r="S37" t="n">
-        <v>6.468578063511188</v>
+        <v>6.468578063511176</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3516,7 +3516,7 @@
         <v>57.36239741264435</v>
       </c>
       <c r="H38" t="n">
-        <v>48.01851541561845</v>
+        <v>48.72337227136661</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3567,7 +3567,7 @@
         <v>247.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>166.3174326828064</v>
+        <v>161.7317758270644</v>
       </c>
     </row>
     <row r="39">
@@ -3580,7 +3580,7 @@
         <v>39.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>16.09991244551929</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
@@ -3589,16 +3589,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>324.959653224157</v>
       </c>
       <c r="I39" t="n">
-        <v>8.307228523697521</v>
+        <v>20.81620732261699</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
         <v>155.932929367851</v>
       </c>
       <c r="S39" t="n">
-        <v>107.7003678891396</v>
+        <v>452.7003678891396</v>
       </c>
       <c r="T39" t="n">
         <v>57.34934068921193</v>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>136.9993129555745</v>
+        <v>132.4136560998326</v>
       </c>
       <c r="C41" t="n">
         <v>104.4745782429939</v>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>117.3553209967828</v>
+        <v>118.0601778525742</v>
       </c>
       <c r="T41" t="n">
         <v>235.5690792160011</v>
@@ -3820,13 +3820,13 @@
         <v>16.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>2.937686897702633</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>191.4287443819146</v>
+        <v>6.139618208889886</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>107.7003678891396</v>
       </c>
       <c r="T42" t="n">
-        <v>57.34934068921193</v>
+        <v>402.3493406892119</v>
       </c>
       <c r="U42" t="n">
         <v>55.16125598660184</v>
       </c>
       <c r="V42" t="n">
-        <v>414.5106671915202</v>
+        <v>69.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>432.3731429098285</v>
+        <v>87.37314290982852</v>
       </c>
       <c r="X42" t="n">
-        <v>419.8627394453875</v>
+        <v>74.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>208.5782164677068</v>
+        <v>54.39139276613435</v>
       </c>
     </row>
     <row r="43">
@@ -3987,7 +3987,7 @@
         <v>59.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>57.36239741264433</v>
+        <v>52.77674055690238</v>
       </c>
       <c r="H44" t="n">
         <v>48.7233722713666</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>117.3553209967824</v>
+        <v>118.0601778525742</v>
       </c>
       <c r="T44" t="n">
         <v>235.5690792160011</v>
@@ -4057,22 +4057,22 @@
         <v>16.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>2.937686897702633</v>
       </c>
       <c r="E45" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>324.9931585165368</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>96.25964924828935</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4114,10 +4114,10 @@
         <v>69.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>173.4852214296654</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>74.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y45" t="n">
         <v>399.3913927661343</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.914147375084</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C2" t="n">
-        <v>56.9398259175144</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D2" t="n">
-        <v>46.49623426110047</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E2" t="n">
-        <v>42.08887102183921</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F2" t="n">
-        <v>37.14985212485754</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G2" t="n">
-        <v>33.76871875540306</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H2" t="n">
         <v>29.92</v>
@@ -4321,25 +4321,25 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>327.1281081337421</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K2" t="n">
-        <v>697.3881081337421</v>
+        <v>400.2796902997726</v>
       </c>
       <c r="L2" t="n">
-        <v>1067.648108133742</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="M2" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="N2" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O2" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P2" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4348,25 +4348,25 @@
         <v>1496</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.815317606417</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.067250178448</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3617021698515</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1889504861909</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W2" t="n">
-        <v>496.4076616165469</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1835874138523</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.7417362190983</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1079.201771408213</v>
+        <v>746.3195099276484</v>
       </c>
       <c r="C3" t="n">
-        <v>714.4543850996074</v>
+        <v>381.5721236190429</v>
       </c>
       <c r="D3" t="n">
-        <v>714.4543850996074</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="E3" t="n">
-        <v>714.4543850996074</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="F3" t="n">
-        <v>371.3874736472065</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="G3" t="n">
-        <v>42.57925177992138</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="H3" t="n">
-        <v>42.57925177992138</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="I3" t="n">
-        <v>33.13396963146437</v>
+        <v>30.1199146314645</v>
       </c>
       <c r="J3" t="n">
-        <v>177.6113405614803</v>
+        <v>174.7984703728012</v>
       </c>
       <c r="K3" t="n">
-        <v>401.8775591086939</v>
+        <v>399.4085458068072</v>
       </c>
       <c r="L3" t="n">
-        <v>720.3885386284223</v>
+        <v>718.3818833454036</v>
       </c>
       <c r="M3" t="n">
-        <v>861.5031803712816</v>
+        <v>860.0360750882628</v>
       </c>
       <c r="N3" t="n">
-        <v>1051.274153846774</v>
+        <v>1050.360878846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.994549492757</v>
+        <v>1341.587921002191</v>
       </c>
       <c r="P3" t="n">
         <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1349.46108157432</v>
+        <v>1349.738421006376</v>
       </c>
       <c r="R3" t="n">
-        <v>1214.459075542376</v>
+        <v>1214.871311105555</v>
       </c>
       <c r="S3" t="n">
-        <v>1151.339064143017</v>
+        <v>1151.791656100326</v>
       </c>
       <c r="T3" t="n">
-        <v>1146.820433372515</v>
+        <v>813.9380289531281</v>
       </c>
       <c r="U3" t="n">
-        <v>1146.622528526128</v>
+        <v>813.7402670455638</v>
       </c>
       <c r="V3" t="n">
-        <v>1131.965288938734</v>
+        <v>799.0830274581697</v>
       </c>
       <c r="W3" t="n">
-        <v>1099.265144585372</v>
+        <v>766.3828831048075</v>
       </c>
       <c r="X3" t="n">
-        <v>1079.201771408213</v>
+        <v>746.3195099276484</v>
       </c>
       <c r="Y3" t="n">
-        <v>1079.201771408213</v>
+        <v>746.3195099276484</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1248.167377013092</v>
+        <v>704.6187527280301</v>
       </c>
       <c r="C4" t="n">
-        <v>1248.167377013092</v>
+        <v>704.6187527280301</v>
       </c>
       <c r="D4" t="n">
-        <v>1248.167377013092</v>
+        <v>704.6187527280301</v>
       </c>
       <c r="E4" t="n">
-        <v>1248.167377013092</v>
+        <v>727.5381897762563</v>
       </c>
       <c r="F4" t="n">
-        <v>1248.167377013092</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="G4" t="n">
-        <v>1401.756037981944</v>
+        <v>851.8991623681918</v>
       </c>
       <c r="H4" t="n">
-        <v>1401.756037981944</v>
+        <v>1023.050610806278</v>
       </c>
       <c r="I4" t="n">
-        <v>1496</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="J4" t="n">
-        <v>1496</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K4" t="n">
-        <v>1496</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L4" t="n">
-        <v>1496</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1403.273682802524</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1258.790761928658</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>1042.177358901337</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>774.2966876474056</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>460.7236912579127</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R4" t="n">
-        <v>139.176451535273</v>
+        <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>179.6001272851838</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T4" t="n">
-        <v>368.4538490669395</v>
+        <v>259.2361373677321</v>
       </c>
       <c r="U4" t="n">
-        <v>615.0149741642425</v>
+        <v>505.7973598420842</v>
       </c>
       <c r="V4" t="n">
-        <v>813.8363670501885</v>
+        <v>704.6187527280301</v>
       </c>
       <c r="W4" t="n">
-        <v>985.7272853098659</v>
+        <v>704.6187527280301</v>
       </c>
       <c r="X4" t="n">
-        <v>1136.75807633406</v>
+        <v>704.6187527280301</v>
       </c>
       <c r="Y4" t="n">
-        <v>1248.167377013092</v>
+        <v>704.6187527280301</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.731003807232</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C5" t="n">
-        <v>58.7566823496624</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D5" t="n">
-        <v>48.31309069324847</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E5" t="n">
-        <v>43.90572745398721</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F5" t="n">
-        <v>38.96670855700554</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G5" t="n">
-        <v>33.76871875540306</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H5" t="n">
         <v>29.92</v>
@@ -4558,25 +4558,25 @@
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>263.0661931588676</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K5" t="n">
-        <v>633.3261931588676</v>
+        <v>400.2796902997726</v>
       </c>
       <c r="L5" t="n">
-        <v>697.388108133742</v>
+        <v>464.9696632645968</v>
       </c>
       <c r="M5" t="n">
-        <v>1067.648108133742</v>
+        <v>835.2296632645968</v>
       </c>
       <c r="N5" t="n">
-        <v>1437.908108133742</v>
+        <v>1205.489663264597</v>
       </c>
       <c r="O5" t="n">
-        <v>1437.908108133742</v>
+        <v>1205.489663264597</v>
       </c>
       <c r="P5" t="n">
-        <v>1496</v>
+        <v>1264.153869653468</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.632174038565</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.884106610596</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U5" t="n">
-        <v>971.1785586019998</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V5" t="n">
-        <v>739.0058069183393</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W5" t="n">
-        <v>498.2245180486953</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X5" t="n">
-        <v>304.0004438460006</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.5585926512467</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.92</v>
+        <v>1225.724928051676</v>
       </c>
       <c r="C6" t="n">
-        <v>29.92</v>
+        <v>860.9775417430701</v>
       </c>
       <c r="D6" t="n">
-        <v>29.92</v>
+        <v>860.9775417430701</v>
       </c>
       <c r="E6" t="n">
-        <v>29.92</v>
+        <v>860.9775417430701</v>
       </c>
       <c r="F6" t="n">
-        <v>29.92</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="G6" t="n">
-        <v>29.92</v>
+        <v>574.8967309533409</v>
       </c>
       <c r="H6" t="n">
-        <v>29.92</v>
+        <v>241.534702729969</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K6" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L6" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M6" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N6" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1346.247111942856</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1211.245105910912</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S6" t="n">
-        <v>1148.125094511552</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T6" t="n">
-        <v>770.3473167337745</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U6" t="n">
-        <v>475.1185348956932</v>
+        <v>1293.145685169591</v>
       </c>
       <c r="V6" t="n">
-        <v>460.4612953082991</v>
+        <v>1278.488445582197</v>
       </c>
       <c r="W6" t="n">
-        <v>427.761150954937</v>
+        <v>1245.788301228835</v>
       </c>
       <c r="X6" t="n">
-        <v>407.6977777777778</v>
+        <v>1225.724928051676</v>
       </c>
       <c r="Y6" t="n">
-        <v>407.6977777777778</v>
+        <v>1225.724928051676</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>909.9815649334121</v>
+        <v>579.2141740099605</v>
       </c>
       <c r="C7" t="n">
-        <v>909.9815649334121</v>
+        <v>705.2161798283963</v>
       </c>
       <c r="D7" t="n">
-        <v>909.9815649334121</v>
+        <v>818.5353239533964</v>
       </c>
       <c r="E7" t="n">
-        <v>1027.810469144825</v>
+        <v>936.3642281648094</v>
       </c>
       <c r="F7" t="n">
-        <v>1027.810469144825</v>
+        <v>1060.725200756745</v>
       </c>
       <c r="G7" t="n">
-        <v>1181.399130113678</v>
+        <v>1214.315646971499</v>
       </c>
       <c r="H7" t="n">
-        <v>1352.534706092747</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="I7" t="n">
-        <v>1352.534706092747</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="J7" t="n">
-        <v>1352.534706092747</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M7" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N7" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O7" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P7" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R7" t="n">
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T7" t="n">
-        <v>29.92</v>
+        <v>109.4863131902839</v>
       </c>
       <c r="U7" t="n">
-        <v>276.481125097303</v>
+        <v>356.0475356646361</v>
       </c>
       <c r="V7" t="n">
-        <v>475.302517983249</v>
+        <v>356.0475356646361</v>
       </c>
       <c r="W7" t="n">
-        <v>647.1934362429264</v>
+        <v>356.0475356646361</v>
       </c>
       <c r="X7" t="n">
-        <v>798.2242272671199</v>
+        <v>356.0475356646361</v>
       </c>
       <c r="Y7" t="n">
-        <v>798.2242272671199</v>
+        <v>467.4568363436684</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.731003807232</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C8" t="n">
-        <v>58.7566823496624</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D8" t="n">
-        <v>48.31309069324847</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E8" t="n">
-        <v>43.90572745398721</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F8" t="n">
-        <v>38.96670855700554</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G8" t="n">
-        <v>33.76871875540306</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H8" t="n">
         <v>29.92</v>
@@ -4795,22 +4795,22 @@
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>263.0661931588676</v>
+        <v>452.3245884924623</v>
       </c>
       <c r="L8" t="n">
-        <v>327.128108133742</v>
+        <v>517.0145614572864</v>
       </c>
       <c r="M8" t="n">
-        <v>697.388108133742</v>
+        <v>887.2745614572864</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.648108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.648108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P8" t="n">
         <v>1125.74</v>
@@ -4819,28 +4819,28 @@
         <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1496</v>
+        <v>1494.026862160817</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U8" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V8" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W8" t="n">
-        <v>498.2245180486953</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X8" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.5585926512467</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="9">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>241.6095073802453</v>
+        <v>847.9471502738977</v>
       </c>
       <c r="C9" t="n">
-        <v>241.6095073802453</v>
+        <v>847.9471502738977</v>
       </c>
       <c r="D9" t="n">
-        <v>241.6095073802453</v>
+        <v>847.9471502738977</v>
       </c>
       <c r="E9" t="n">
-        <v>241.6095073802453</v>
+        <v>501.8137187366122</v>
       </c>
       <c r="F9" t="n">
-        <v>241.6095073802453</v>
+        <v>501.8137187366122</v>
       </c>
       <c r="G9" t="n">
-        <v>241.6095073802453</v>
+        <v>501.8137187366122</v>
       </c>
       <c r="H9" t="n">
-        <v>241.6095073802453</v>
+        <v>241.534702729969</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K9" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L9" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M9" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N9" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P9" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1346.247111942856</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R9" t="n">
-        <v>968.469334165078</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S9" t="n">
-        <v>905.3493227657184</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T9" t="n">
-        <v>900.8306919952165</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U9" t="n">
-        <v>900.6327871488301</v>
+        <v>1293.145685169591</v>
       </c>
       <c r="V9" t="n">
-        <v>885.975547561436</v>
+        <v>1278.488445582197</v>
       </c>
       <c r="W9" t="n">
-        <v>853.2754032080738</v>
+        <v>1245.788301228835</v>
       </c>
       <c r="X9" t="n">
-        <v>475.497625430296</v>
+        <v>1225.724928051676</v>
       </c>
       <c r="Y9" t="n">
-        <v>475.497625430296</v>
+        <v>1225.724928051676</v>
       </c>
     </row>
     <row r="10">
@@ -4929,52 +4929,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1021.390865612444</v>
+        <v>141.6773376662921</v>
       </c>
       <c r="C10" t="n">
-        <v>1147.39287143088</v>
+        <v>267.679343484728</v>
       </c>
       <c r="D10" t="n">
-        <v>1251.462556240126</v>
+        <v>380.998487609728</v>
       </c>
       <c r="E10" t="n">
-        <v>1251.462556240126</v>
+        <v>498.8273918211411</v>
       </c>
       <c r="F10" t="n">
-        <v>1251.462556240126</v>
+        <v>623.1883644130766</v>
       </c>
       <c r="G10" t="n">
-        <v>1251.462556240126</v>
+        <v>776.7788106278307</v>
       </c>
       <c r="H10" t="n">
-        <v>1251.462556240126</v>
+        <v>947.9302590659167</v>
       </c>
       <c r="I10" t="n">
-        <v>1251.462556240126</v>
+        <v>1174.592920952819</v>
       </c>
       <c r="J10" t="n">
-        <v>1251.462556240126</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K10" t="n">
-        <v>1382.983127881912</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L10" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M10" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N10" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O10" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P10" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R10" t="n">
         <v>29.92</v>
@@ -4986,19 +4986,19 @@
         <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>276.481125097303</v>
+        <v>29.92</v>
       </c>
       <c r="V10" t="n">
-        <v>475.302517983249</v>
+        <v>29.92</v>
       </c>
       <c r="W10" t="n">
-        <v>647.1934362429264</v>
+        <v>29.92</v>
       </c>
       <c r="X10" t="n">
-        <v>798.2242272671199</v>
+        <v>29.92</v>
       </c>
       <c r="Y10" t="n">
-        <v>909.6335279461522</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>596.5184060421567</v>
+        <v>596.4384060421568</v>
       </c>
       <c r="C11" t="n">
-        <v>466.7461047866073</v>
+        <v>466.6661047866074</v>
       </c>
       <c r="D11" t="n">
-        <v>376.5045333322136</v>
+        <v>376.4245333322136</v>
       </c>
       <c r="E11" t="n">
-        <v>292.2991902949725</v>
+        <v>292.2191902949726</v>
       </c>
       <c r="F11" t="n">
-        <v>207.562191600011</v>
+        <v>207.4821916000111</v>
       </c>
       <c r="G11" t="n">
-        <v>125.3779517892592</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H11" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I11" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J11" t="n">
-        <v>560.4418942939371</v>
+        <v>134.360205073642</v>
       </c>
       <c r="K11" t="n">
-        <v>736.1134691180577</v>
+        <v>775.8802050736419</v>
       </c>
       <c r="L11" t="n">
-        <v>954.0495916306205</v>
+        <v>1417.400205073642</v>
       </c>
       <c r="M11" t="n">
-        <v>954.0495916306206</v>
+        <v>2058.920205073645</v>
       </c>
       <c r="N11" t="n">
-        <v>1596.559591630621</v>
+        <v>2230.549243836214</v>
       </c>
       <c r="O11" t="n">
-        <v>1809.956778005698</v>
+        <v>2393.691050093541</v>
       </c>
       <c r="P11" t="n">
-        <v>2008.265727912157</v>
+        <v>2592</v>
       </c>
       <c r="Q11" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R11" t="n">
-        <v>2595.065916015951</v>
+        <v>2592</v>
       </c>
       <c r="S11" t="n">
-        <v>2451.570786871937</v>
+        <v>2448.504870855986</v>
       </c>
       <c r="T11" t="n">
-        <v>2189.379797764865</v>
+        <v>2186.313881748914</v>
       </c>
       <c r="U11" t="n">
-        <v>1857.955859826824</v>
+        <v>1857.875859826824</v>
       </c>
       <c r="V11" t="n">
-        <v>1545.985128345183</v>
+        <v>1545.905128345183</v>
       </c>
       <c r="W11" t="n">
-        <v>1225.405859677559</v>
+        <v>1225.325859677559</v>
       </c>
       <c r="X11" t="n">
-        <v>951.383805676885</v>
+        <v>951.3038056768851</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.1439746841512</v>
+        <v>759.0639746841513</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1001.877593356413</v>
+        <v>1247.449260026979</v>
       </c>
       <c r="C12" t="n">
-        <v>961.372631290232</v>
+        <v>1206.944297960798</v>
       </c>
       <c r="D12" t="n">
-        <v>609.9204223026536</v>
+        <v>1073.315910404529</v>
       </c>
       <c r="E12" t="n">
-        <v>403.0200546248188</v>
+        <v>727.1824788672432</v>
       </c>
       <c r="F12" t="n">
-        <v>59.95314317241791</v>
+        <v>384.1155674148422</v>
       </c>
       <c r="G12" t="n">
-        <v>55.91964972137067</v>
+        <v>55.83964972137069</v>
       </c>
       <c r="H12" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I12" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J12" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K12" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L12" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M12" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N12" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O12" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P12" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2253.229505368536</v>
+        <v>2174.558747796677</v>
       </c>
       <c r="R12" t="n">
-        <v>2071.479071663636</v>
+        <v>1992.808314091777</v>
       </c>
       <c r="S12" t="n">
-        <v>1938.448397028141</v>
+        <v>1859.777639456283</v>
       </c>
       <c r="T12" t="n">
-        <v>1856.277345826917</v>
+        <v>1777.606588255059</v>
       </c>
       <c r="U12" t="n">
-        <v>1776.316481193986</v>
+        <v>1697.645723622128</v>
       </c>
       <c r="V12" t="n">
-        <v>1681.861261808612</v>
+        <v>1603.190504236754</v>
       </c>
       <c r="W12" t="n">
-        <v>1569.36313765727</v>
+        <v>1490.692380085412</v>
       </c>
       <c r="X12" t="n">
-        <v>1469.501784682131</v>
+        <v>1390.831027110273</v>
       </c>
       <c r="Y12" t="n">
-        <v>1066.07613542341</v>
+        <v>1311.647802093976</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>686.6672726401017</v>
+        <v>686.5872726401018</v>
       </c>
       <c r="C13" t="n">
-        <v>734.4592784585375</v>
+        <v>734.3792784585376</v>
       </c>
       <c r="D13" t="n">
-        <v>769.5684225835375</v>
+        <v>769.4884225835376</v>
       </c>
       <c r="E13" t="n">
-        <v>809.1873267949505</v>
+        <v>809.1073267949506</v>
       </c>
       <c r="F13" t="n">
-        <v>855.338299386886</v>
+        <v>855.2582993868861</v>
       </c>
       <c r="G13" t="n">
-        <v>931.1543456016401</v>
+        <v>931.0743456016402</v>
       </c>
       <c r="H13" t="n">
-        <v>1027.968674039726</v>
+        <v>1027.888674039726</v>
       </c>
       <c r="I13" t="n">
-        <v>1189.521015926629</v>
+        <v>1189.441015926629</v>
       </c>
       <c r="J13" t="n">
-        <v>1516.192015759408</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K13" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L13" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M13" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N13" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O13" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P13" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568782</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380923</v>
       </c>
       <c r="R13" t="n">
-        <v>82.69634147829413</v>
+        <v>82.61634147829412</v>
       </c>
       <c r="S13" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T13" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506081</v>
       </c>
       <c r="U13" t="n">
-        <v>332.8075321249603</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V13" t="n">
-        <v>453.4189250109063</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W13" t="n">
-        <v>547.0998432705837</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X13" t="n">
-        <v>619.9206342947773</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y13" t="n">
-        <v>653.1199349738096</v>
+        <v>653.0399349738096</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>596.5184060421567</v>
+        <v>596.4384060421568</v>
       </c>
       <c r="C14" t="n">
-        <v>466.7461047866073</v>
+        <v>466.6661047866073</v>
       </c>
       <c r="D14" t="n">
-        <v>376.5045333322136</v>
+        <v>376.4245333322136</v>
       </c>
       <c r="E14" t="n">
-        <v>292.2991902949725</v>
+        <v>292.2191902949725</v>
       </c>
       <c r="F14" t="n">
-        <v>207.562191600011</v>
+        <v>207.482191600011</v>
       </c>
       <c r="G14" t="n">
-        <v>125.3779517892592</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H14" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I14" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J14" t="n">
-        <v>560.4418942939371</v>
+        <v>134.360205073642</v>
       </c>
       <c r="K14" t="n">
-        <v>736.1134691180577</v>
+        <v>310.0317798977626</v>
       </c>
       <c r="L14" t="n">
-        <v>954.0495916306205</v>
+        <v>947.509243836214</v>
       </c>
       <c r="M14" t="n">
-        <v>1596.559591630621</v>
+        <v>1589.029243836214</v>
       </c>
       <c r="N14" t="n">
-        <v>2234.549243836214</v>
+        <v>2230.549243836214</v>
       </c>
       <c r="O14" t="n">
-        <v>2397.691050093541</v>
+        <v>2393.691050093541</v>
       </c>
       <c r="P14" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="Q14" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R14" t="n">
-        <v>2595.065916015951</v>
+        <v>2592</v>
       </c>
       <c r="S14" t="n">
-        <v>2451.570786871937</v>
+        <v>2451.490786871937</v>
       </c>
       <c r="T14" t="n">
-        <v>2189.379797764865</v>
+        <v>2189.299797764865</v>
       </c>
       <c r="U14" t="n">
-        <v>1857.955859826824</v>
+        <v>1857.875859826824</v>
       </c>
       <c r="V14" t="n">
-        <v>1545.985128345183</v>
+        <v>1545.905128345183</v>
       </c>
       <c r="W14" t="n">
-        <v>1225.405859677559</v>
+        <v>1225.325859677559</v>
       </c>
       <c r="X14" t="n">
-        <v>951.383805676885</v>
+        <v>951.3038056768851</v>
       </c>
       <c r="Y14" t="n">
-        <v>759.1439746841512</v>
+        <v>759.0639746841513</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>816.8682329734396</v>
+        <v>816.7882329734394</v>
       </c>
       <c r="C15" t="n">
-        <v>776.3632709072585</v>
+        <v>776.2832709072584</v>
       </c>
       <c r="D15" t="n">
-        <v>424.9110619196801</v>
+        <v>749.0734861621042</v>
       </c>
       <c r="E15" t="n">
-        <v>403.0200546248188</v>
+        <v>402.9400546248188</v>
       </c>
       <c r="F15" t="n">
-        <v>59.95314317241791</v>
+        <v>59.87314317241791</v>
       </c>
       <c r="G15" t="n">
-        <v>55.91964972137067</v>
+        <v>55.83964972137068</v>
       </c>
       <c r="H15" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I15" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J15" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K15" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L15" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M15" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N15" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O15" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P15" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>2174.638747796677</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R15" t="n">
-        <v>1992.888314091777</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S15" t="n">
-        <v>1859.857639456283</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T15" t="n">
-        <v>1777.686588255059</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U15" t="n">
-        <v>1697.725723622128</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V15" t="n">
-        <v>1603.270504236754</v>
+        <v>1681.781261808612</v>
       </c>
       <c r="W15" t="n">
-        <v>1490.772380085412</v>
+        <v>1569.28313765727</v>
       </c>
       <c r="X15" t="n">
-        <v>1390.911027110273</v>
+        <v>1469.421784682131</v>
       </c>
       <c r="Y15" t="n">
-        <v>1205.30919928286</v>
+        <v>1205.22919928286</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>686.6672726401017</v>
+        <v>681.4588756890412</v>
       </c>
       <c r="C16" t="n">
-        <v>734.4592784585375</v>
+        <v>729.2508815074769</v>
       </c>
       <c r="D16" t="n">
-        <v>764.4400256324769</v>
+        <v>764.360025632477</v>
       </c>
       <c r="E16" t="n">
-        <v>804.0589298438899</v>
+        <v>803.97892984389</v>
       </c>
       <c r="F16" t="n">
-        <v>850.2099024358254</v>
+        <v>850.1299024358254</v>
       </c>
       <c r="G16" t="n">
-        <v>926.0259486505795</v>
+        <v>925.9459486505796</v>
       </c>
       <c r="H16" t="n">
-        <v>1022.840277088666</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I16" t="n">
-        <v>1184.392618975568</v>
+        <v>1184.312618975568</v>
       </c>
       <c r="J16" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K16" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L16" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M16" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N16" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O16" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P16" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568782</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380924</v>
       </c>
       <c r="R16" t="n">
-        <v>82.69634147829413</v>
+        <v>82.61634147829413</v>
       </c>
       <c r="S16" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T16" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506081</v>
       </c>
       <c r="U16" t="n">
-        <v>332.8075321249603</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V16" t="n">
-        <v>453.4189250109063</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W16" t="n">
-        <v>547.0998432705837</v>
+        <v>541.8914463195232</v>
       </c>
       <c r="X16" t="n">
-        <v>619.9206342947773</v>
+        <v>614.7122373437168</v>
       </c>
       <c r="Y16" t="n">
-        <v>653.1199349738096</v>
+        <v>647.911538022749</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>596.5184060421567</v>
+        <v>596.4384060421568</v>
       </c>
       <c r="C17" t="n">
-        <v>466.7461047866073</v>
+        <v>466.6661047866073</v>
       </c>
       <c r="D17" t="n">
-        <v>376.5045333322136</v>
+        <v>376.4245333322136</v>
       </c>
       <c r="E17" t="n">
-        <v>292.2991902949725</v>
+        <v>292.2191902949725</v>
       </c>
       <c r="F17" t="n">
-        <v>207.562191600011</v>
+        <v>207.482191600011</v>
       </c>
       <c r="G17" t="n">
-        <v>125.3779517892592</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H17" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I17" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J17" t="n">
-        <v>560.4418942939371</v>
+        <v>134.360205073642</v>
       </c>
       <c r="K17" t="n">
-        <v>736.1134691180577</v>
+        <v>729.5731213236512</v>
       </c>
       <c r="L17" t="n">
-        <v>954.0495916306205</v>
+        <v>947.509243836214</v>
       </c>
       <c r="M17" t="n">
-        <v>1596.559591630621</v>
+        <v>1589.029243836214</v>
       </c>
       <c r="N17" t="n">
-        <v>2234.549243836214</v>
+        <v>2230.549243836214</v>
       </c>
       <c r="O17" t="n">
-        <v>2397.691050093541</v>
+        <v>2393.691050093541</v>
       </c>
       <c r="P17" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="Q17" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R17" t="n">
-        <v>2595.065916015951</v>
+        <v>2592</v>
       </c>
       <c r="S17" t="n">
-        <v>2451.570786871937</v>
+        <v>2448.504870855986</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.379797764865</v>
+        <v>2186.313881748914</v>
       </c>
       <c r="U17" t="n">
-        <v>1857.955859826824</v>
+        <v>1854.889943810872</v>
       </c>
       <c r="V17" t="n">
-        <v>1545.985128345183</v>
+        <v>1542.919212329232</v>
       </c>
       <c r="W17" t="n">
-        <v>1225.405859677559</v>
+        <v>1225.325859677559</v>
       </c>
       <c r="X17" t="n">
-        <v>951.383805676885</v>
+        <v>951.3038056768851</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.1439746841512</v>
+        <v>759.0639746841513</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1247.529260026979</v>
+        <v>1326.040017598837</v>
       </c>
       <c r="C18" t="n">
-        <v>1100.605695149683</v>
+        <v>1100.525695149683</v>
       </c>
       <c r="D18" t="n">
-        <v>749.1534861621044</v>
+        <v>749.0734861621042</v>
       </c>
       <c r="E18" t="n">
-        <v>403.0200546248188</v>
+        <v>402.9400546248188</v>
       </c>
       <c r="F18" t="n">
-        <v>59.95314317241791</v>
+        <v>59.87314317241791</v>
       </c>
       <c r="G18" t="n">
-        <v>55.91964972137067</v>
+        <v>55.83964972137068</v>
       </c>
       <c r="H18" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I18" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J18" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K18" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L18" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M18" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N18" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O18" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P18" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>2174.638747796677</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R18" t="n">
-        <v>1992.888314091777</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S18" t="n">
-        <v>1859.857639456283</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T18" t="n">
-        <v>1777.686588255059</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U18" t="n">
-        <v>1697.725723622128</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V18" t="n">
-        <v>1603.270504236754</v>
+        <v>1681.781261808612</v>
       </c>
       <c r="W18" t="n">
-        <v>1490.772380085412</v>
+        <v>1569.28313765727</v>
       </c>
       <c r="X18" t="n">
-        <v>1390.911027110273</v>
+        <v>1469.421784682131</v>
       </c>
       <c r="Y18" t="n">
-        <v>1311.727802093975</v>
+        <v>1390.238559665834</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>686.6672726401017</v>
+        <v>681.4588756890412</v>
       </c>
       <c r="C19" t="n">
-        <v>734.4592784585375</v>
+        <v>729.2508815074769</v>
       </c>
       <c r="D19" t="n">
-        <v>764.4400256324769</v>
+        <v>764.360025632477</v>
       </c>
       <c r="E19" t="n">
-        <v>804.0589298438899</v>
+        <v>803.97892984389</v>
       </c>
       <c r="F19" t="n">
-        <v>850.2099024358254</v>
+        <v>850.1299024358254</v>
       </c>
       <c r="G19" t="n">
-        <v>926.0259486505795</v>
+        <v>925.9459486505796</v>
       </c>
       <c r="H19" t="n">
-        <v>1022.840277088666</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I19" t="n">
-        <v>1184.392618975568</v>
+        <v>1184.312618975568</v>
       </c>
       <c r="J19" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K19" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L19" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M19" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N19" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O19" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P19" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568782</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380924</v>
       </c>
       <c r="R19" t="n">
-        <v>82.69634147829413</v>
+        <v>82.61634147829413</v>
       </c>
       <c r="S19" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T19" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506081</v>
       </c>
       <c r="U19" t="n">
-        <v>332.8075321249603</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V19" t="n">
-        <v>453.4189250109063</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W19" t="n">
-        <v>547.0998432705837</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X19" t="n">
-        <v>619.9206342947773</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y19" t="n">
-        <v>653.1199349738096</v>
+        <v>653.0399349738096</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>596.5184060421567</v>
+        <v>596.4384060421568</v>
       </c>
       <c r="C20" t="n">
-        <v>466.7461047866073</v>
+        <v>466.6661047866073</v>
       </c>
       <c r="D20" t="n">
-        <v>376.5045333322136</v>
+        <v>376.4245333322136</v>
       </c>
       <c r="E20" t="n">
-        <v>292.2991902949725</v>
+        <v>292.2191902949725</v>
       </c>
       <c r="F20" t="n">
-        <v>207.562191600011</v>
+        <v>207.482191600011</v>
       </c>
       <c r="G20" t="n">
-        <v>125.3779517892592</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H20" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I20" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J20" t="n">
-        <v>134.440205073642</v>
+        <v>134.360205073642</v>
       </c>
       <c r="K20" t="n">
-        <v>731.5931213236511</v>
+        <v>729.5731213236512</v>
       </c>
       <c r="L20" t="n">
-        <v>949.5292438362139</v>
+        <v>947.509243836214</v>
       </c>
       <c r="M20" t="n">
-        <v>1592.039243836214</v>
+        <v>1589.029243836214</v>
       </c>
       <c r="N20" t="n">
-        <v>2234.549243836214</v>
+        <v>2230.549243836214</v>
       </c>
       <c r="O20" t="n">
-        <v>2397.691050093541</v>
+        <v>2393.691050093541</v>
       </c>
       <c r="P20" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="Q20" t="n">
-        <v>2596</v>
+        <v>2592</v>
       </c>
       <c r="R20" t="n">
-        <v>2595.065916015951</v>
+        <v>2592</v>
       </c>
       <c r="S20" t="n">
-        <v>2451.570786871937</v>
+        <v>2451.490786871937</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.379797764865</v>
+        <v>2189.299797764865</v>
       </c>
       <c r="U20" t="n">
-        <v>1857.955859826824</v>
+        <v>1857.875859826824</v>
       </c>
       <c r="V20" t="n">
-        <v>1545.985128345183</v>
+        <v>1545.905128345183</v>
       </c>
       <c r="W20" t="n">
-        <v>1225.405859677559</v>
+        <v>1225.325859677559</v>
       </c>
       <c r="X20" t="n">
-        <v>951.383805676885</v>
+        <v>951.3038056768851</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.1439746841512</v>
+        <v>759.0639746841513</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>168.383384488591</v>
+        <v>168.3033844885911</v>
       </c>
       <c r="C21" t="n">
-        <v>127.87842242241</v>
+        <v>127.79842242241</v>
       </c>
       <c r="D21" t="n">
-        <v>100.6686376772558</v>
+        <v>100.5886376772558</v>
       </c>
       <c r="E21" t="n">
-        <v>78.77763038239453</v>
+        <v>78.69763038239455</v>
       </c>
       <c r="F21" t="n">
-        <v>59.95314317241791</v>
+        <v>59.87314317241791</v>
       </c>
       <c r="G21" t="n">
-        <v>55.91964972137067</v>
+        <v>55.83964972137068</v>
       </c>
       <c r="H21" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I21" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J21" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K21" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L21" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M21" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N21" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O21" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P21" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>2174.638747796677</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R21" t="n">
-        <v>1992.888314091777</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S21" t="n">
-        <v>1859.857639456283</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T21" t="n">
-        <v>1777.686588255059</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U21" t="n">
-        <v>1373.483299379703</v>
+        <v>1591.227120811013</v>
       </c>
       <c r="V21" t="n">
-        <v>954.7856557519051</v>
+        <v>1172.529477183214</v>
       </c>
       <c r="W21" t="n">
-        <v>518.0451073581389</v>
+        <v>735.7889287894482</v>
       </c>
       <c r="X21" t="n">
-        <v>311.765151571885</v>
+        <v>311.685151571885</v>
       </c>
       <c r="Y21" t="n">
-        <v>232.5819265555876</v>
+        <v>232.5019265555877</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>681.5388756890411</v>
+        <v>686.5872726401018</v>
       </c>
       <c r="C22" t="n">
-        <v>729.3308815074769</v>
+        <v>734.3792784585376</v>
       </c>
       <c r="D22" t="n">
-        <v>764.4400256324769</v>
+        <v>769.4884225835376</v>
       </c>
       <c r="E22" t="n">
-        <v>804.0589298438899</v>
+        <v>803.97892984389</v>
       </c>
       <c r="F22" t="n">
-        <v>850.2099024358254</v>
+        <v>850.1299024358254</v>
       </c>
       <c r="G22" t="n">
-        <v>926.0259486505795</v>
+        <v>925.9459486505796</v>
       </c>
       <c r="H22" t="n">
-        <v>1022.840277088666</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I22" t="n">
-        <v>1184.392618975568</v>
+        <v>1184.312618975568</v>
       </c>
       <c r="J22" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K22" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L22" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M22" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N22" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O22" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568782</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380924</v>
       </c>
       <c r="R22" t="n">
-        <v>82.69634147829413</v>
+        <v>82.61634147829413</v>
       </c>
       <c r="S22" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T22" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506081</v>
       </c>
       <c r="U22" t="n">
-        <v>332.8075321249603</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V22" t="n">
-        <v>453.4189250109063</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W22" t="n">
-        <v>547.0998432705837</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X22" t="n">
-        <v>619.9206342947773</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y22" t="n">
-        <v>653.1199349738096</v>
+        <v>653.0399349738096</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>596.5184060421568</v>
+        <v>596.4384060421568</v>
       </c>
       <c r="C23" t="n">
-        <v>466.7461047866074</v>
+        <v>466.6661047866073</v>
       </c>
       <c r="D23" t="n">
-        <v>376.5045333322136</v>
+        <v>376.4245333322136</v>
       </c>
       <c r="E23" t="n">
-        <v>292.2991902949726</v>
+        <v>292.2191902949725</v>
       </c>
       <c r="F23" t="n">
-        <v>207.5621916000111</v>
+        <v>207.482191600011</v>
       </c>
       <c r="G23" t="n">
-        <v>125.3779517892592</v>
+        <v>125.2979517892592</v>
       </c>
       <c r="H23" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I23" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J23" t="n">
-        <v>560.4418942939371</v>
+        <v>134.360205073642</v>
       </c>
       <c r="K23" t="n">
-        <v>736.1134691180577</v>
+        <v>729.5731213236611</v>
       </c>
       <c r="L23" t="n">
-        <v>954.0495916306205</v>
+        <v>947.5092438362238</v>
       </c>
       <c r="M23" t="n">
-        <v>1596.559591630621</v>
+        <v>1589.029243836228</v>
       </c>
       <c r="N23" t="n">
-        <v>2234.549243836214</v>
+        <v>2230.549243836233</v>
       </c>
       <c r="O23" t="n">
-        <v>2397.691050093541</v>
+        <v>2393.69105009356</v>
       </c>
       <c r="P23" t="n">
-        <v>2596</v>
+        <v>2592.000000000019</v>
       </c>
       <c r="Q23" t="n">
-        <v>2596</v>
+        <v>2592.000000000019</v>
       </c>
       <c r="R23" t="n">
-        <v>2595.065916015951</v>
+        <v>2592.000000000019</v>
       </c>
       <c r="S23" t="n">
-        <v>2451.570786871937</v>
+        <v>2448.504870856005</v>
       </c>
       <c r="T23" t="n">
-        <v>2189.379797764865</v>
+        <v>2186.313881748933</v>
       </c>
       <c r="U23" t="n">
-        <v>1857.955859826824</v>
+        <v>1854.889943810892</v>
       </c>
       <c r="V23" t="n">
-        <v>1545.985128345183</v>
+        <v>1542.919212329251</v>
       </c>
       <c r="W23" t="n">
-        <v>1225.405859677559</v>
+        <v>1225.325859677559</v>
       </c>
       <c r="X23" t="n">
-        <v>951.383805676885</v>
+        <v>951.3038056768851</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.1439746841513</v>
+        <v>759.0639746841513</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1247.529260026979</v>
+        <v>1141.030657215864</v>
       </c>
       <c r="C24" t="n">
-        <v>1100.605695149683</v>
+        <v>776.2832709072584</v>
       </c>
       <c r="D24" t="n">
-        <v>749.1534861621044</v>
+        <v>749.0734861621042</v>
       </c>
       <c r="E24" t="n">
-        <v>403.0200546248188</v>
+        <v>402.9400546248188</v>
       </c>
       <c r="F24" t="n">
-        <v>59.95314317241794</v>
+        <v>59.87314317241791</v>
       </c>
       <c r="G24" t="n">
-        <v>55.91964972137069</v>
+        <v>55.83964972137068</v>
       </c>
       <c r="H24" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="I24" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="J24" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036009</v>
       </c>
       <c r="K24" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149654</v>
       </c>
       <c r="L24" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573354</v>
       </c>
       <c r="M24" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N24" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.67128421531</v>
       </c>
       <c r="O24" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672614</v>
       </c>
       <c r="P24" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>2174.638747796677</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R24" t="n">
-        <v>1992.888314091777</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S24" t="n">
-        <v>1859.857639456283</v>
+        <v>1938.368397028141</v>
       </c>
       <c r="T24" t="n">
-        <v>1777.686588255059</v>
+        <v>1856.197345826917</v>
       </c>
       <c r="U24" t="n">
-        <v>1697.725723622128</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V24" t="n">
-        <v>1603.270504236754</v>
+        <v>1681.781261808612</v>
       </c>
       <c r="W24" t="n">
-        <v>1490.772380085412</v>
+        <v>1569.28313765727</v>
       </c>
       <c r="X24" t="n">
-        <v>1390.911027110273</v>
+        <v>1469.421784682131</v>
       </c>
       <c r="Y24" t="n">
-        <v>1311.727802093975</v>
+        <v>1390.238559665834</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>686.6672726401017</v>
+        <v>686.5872726401018</v>
       </c>
       <c r="C25" t="n">
-        <v>734.4592784585375</v>
+        <v>734.3792784585376</v>
       </c>
       <c r="D25" t="n">
-        <v>769.5684225835375</v>
+        <v>769.4884225835376</v>
       </c>
       <c r="E25" t="n">
-        <v>809.1873267949505</v>
+        <v>809.1073267949506</v>
       </c>
       <c r="F25" t="n">
-        <v>855.338299386886</v>
+        <v>855.2582993868861</v>
       </c>
       <c r="G25" t="n">
-        <v>931.1543456016401</v>
+        <v>931.0743456016402</v>
       </c>
       <c r="H25" t="n">
-        <v>1027.968674039726</v>
+        <v>1027.888674039726</v>
       </c>
       <c r="I25" t="n">
-        <v>1189.521015926629</v>
+        <v>1189.441015926629</v>
       </c>
       <c r="J25" t="n">
-        <v>1511.063618808347</v>
+        <v>1516.112015759408</v>
       </c>
       <c r="K25" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564888</v>
       </c>
       <c r="L25" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221213</v>
       </c>
       <c r="M25" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499644</v>
       </c>
       <c r="N25" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241608</v>
       </c>
       <c r="O25" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568782</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380924</v>
       </c>
       <c r="R25" t="n">
-        <v>82.69634147829412</v>
+        <v>82.61634147829413</v>
       </c>
       <c r="S25" t="n">
-        <v>51.92</v>
+        <v>51.84</v>
       </c>
       <c r="T25" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506081</v>
       </c>
       <c r="U25" t="n">
-        <v>332.8075321249603</v>
+        <v>332.7275321249604</v>
       </c>
       <c r="V25" t="n">
-        <v>453.4189250109063</v>
+        <v>453.3389250109063</v>
       </c>
       <c r="W25" t="n">
-        <v>547.0998432705837</v>
+        <v>547.0198432705838</v>
       </c>
       <c r="X25" t="n">
-        <v>619.9206342947773</v>
+        <v>619.8406342947774</v>
       </c>
       <c r="Y25" t="n">
-        <v>653.1199349738096</v>
+        <v>653.0399349738096</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>597.4524900262059</v>
+        <v>593.4524900262406</v>
       </c>
       <c r="C26" t="n">
-        <v>467.6801887706564</v>
+        <v>463.6801887706912</v>
       </c>
       <c r="D26" t="n">
-        <v>377.4386173162627</v>
+        <v>373.4386173162974</v>
       </c>
       <c r="E26" t="n">
-        <v>293.2332742790216</v>
+        <v>289.2332742790564</v>
       </c>
       <c r="F26" t="n">
-        <v>208.4962755840601</v>
+        <v>204.4962755840949</v>
       </c>
       <c r="G26" t="n">
-        <v>126.3120357733083</v>
+        <v>125.2979517892599</v>
       </c>
       <c r="H26" t="n">
-        <v>52.85408398404904</v>
+        <v>51.8400000000007</v>
       </c>
       <c r="I26" t="n">
-        <v>51.92</v>
+        <v>51.8400000000007</v>
       </c>
       <c r="J26" t="n">
-        <v>560.4418942939371</v>
+        <v>560.3618942939378</v>
       </c>
       <c r="K26" t="n">
-        <v>1202.951894293937</v>
+        <v>1201.881894293946</v>
       </c>
       <c r="L26" t="n">
-        <v>1420.8880168065</v>
+        <v>1419.818016806509</v>
       </c>
       <c r="M26" t="n">
-        <v>2063.3980168065</v>
+        <v>1419.818016806509</v>
       </c>
       <c r="N26" t="n">
-        <v>2234.549243836214</v>
+        <v>1752.171050093551</v>
       </c>
       <c r="O26" t="n">
-        <v>2397.691050093541</v>
+        <v>2393.691050093554</v>
       </c>
       <c r="P26" t="n">
-        <v>2596</v>
+        <v>2592.000000000013</v>
       </c>
       <c r="Q26" t="n">
-        <v>2596</v>
+        <v>2592.000000000013</v>
       </c>
       <c r="R26" t="n">
-        <v>2596</v>
+        <v>2592.000000000035</v>
       </c>
       <c r="S26" t="n">
-        <v>2452.504870855986</v>
+        <v>2448.504870856021</v>
       </c>
       <c r="T26" t="n">
-        <v>2190.313881748914</v>
+        <v>2186.313881748949</v>
       </c>
       <c r="U26" t="n">
-        <v>1858.889943810873</v>
+        <v>1854.889943810907</v>
       </c>
       <c r="V26" t="n">
-        <v>1546.919212329232</v>
+        <v>1542.919212329267</v>
       </c>
       <c r="W26" t="n">
-        <v>1226.339943661608</v>
+        <v>1222.339943661643</v>
       </c>
       <c r="X26" t="n">
-        <v>952.317889660934</v>
+        <v>948.3178896609688</v>
       </c>
       <c r="Y26" t="n">
-        <v>760.0780586682004</v>
+        <v>756.0780586682351</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>168.3833844885911</v>
+        <v>1001.797593356413</v>
       </c>
       <c r="C27" t="n">
-        <v>127.87842242241</v>
+        <v>637.050207047808</v>
       </c>
       <c r="D27" t="n">
-        <v>100.6686376772558</v>
+        <v>424.8310619196808</v>
       </c>
       <c r="E27" t="n">
-        <v>78.77763038239456</v>
+        <v>402.9400546248195</v>
       </c>
       <c r="F27" t="n">
-        <v>59.95314317241794</v>
+        <v>59.87314317241861</v>
       </c>
       <c r="G27" t="n">
-        <v>55.91964972137069</v>
+        <v>55.83964972137137</v>
       </c>
       <c r="H27" t="n">
-        <v>51.92</v>
+        <v>51.8400000000007</v>
       </c>
       <c r="I27" t="n">
-        <v>51.92</v>
+        <v>51.8400000000007</v>
       </c>
       <c r="J27" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036016</v>
       </c>
       <c r="K27" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149661</v>
       </c>
       <c r="L27" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573361</v>
       </c>
       <c r="M27" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N27" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.671284215311</v>
       </c>
       <c r="O27" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672615</v>
       </c>
       <c r="P27" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R27" t="n">
-        <v>2071.479071663636</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S27" t="n">
-        <v>1938.448397028141</v>
+        <v>1938.368397028142</v>
       </c>
       <c r="T27" t="n">
-        <v>1856.277345826917</v>
+        <v>1856.197345826918</v>
       </c>
       <c r="U27" t="n">
-        <v>1776.316481193986</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V27" t="n">
-        <v>1681.861261808612</v>
+        <v>1681.781261808612</v>
       </c>
       <c r="W27" t="n">
-        <v>1384.353777274297</v>
+        <v>1569.283137657271</v>
       </c>
       <c r="X27" t="n">
-        <v>960.2500000567335</v>
+        <v>1469.421784682132</v>
       </c>
       <c r="Y27" t="n">
-        <v>556.8243507980119</v>
+        <v>1390.238559665834</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>686.6672726401017</v>
+        <v>681.4588756890419</v>
       </c>
       <c r="C28" t="n">
-        <v>734.4592784585375</v>
+        <v>729.2508815074776</v>
       </c>
       <c r="D28" t="n">
-        <v>769.5684225835375</v>
+        <v>764.3600256324777</v>
       </c>
       <c r="E28" t="n">
-        <v>809.1873267949505</v>
+        <v>803.9789298438907</v>
       </c>
       <c r="F28" t="n">
-        <v>850.2099024358254</v>
+        <v>850.1299024358261</v>
       </c>
       <c r="G28" t="n">
-        <v>926.0259486505795</v>
+        <v>925.9459486505802</v>
       </c>
       <c r="H28" t="n">
-        <v>1022.840277088666</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I28" t="n">
-        <v>1184.392618975568</v>
+        <v>1184.312618975569</v>
       </c>
       <c r="J28" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K28" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564889</v>
       </c>
       <c r="L28" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221214</v>
       </c>
       <c r="M28" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499645</v>
       </c>
       <c r="N28" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241609</v>
       </c>
       <c r="O28" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P28" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568789</v>
       </c>
       <c r="Q28" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380931</v>
       </c>
       <c r="R28" t="n">
-        <v>82.69634147829412</v>
+        <v>82.61634147829483</v>
       </c>
       <c r="S28" t="n">
-        <v>51.92</v>
+        <v>51.8400000000007</v>
       </c>
       <c r="T28" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506088</v>
       </c>
       <c r="U28" t="n">
-        <v>332.8075321249603</v>
+        <v>327.5991351739005</v>
       </c>
       <c r="V28" t="n">
-        <v>453.4189250109063</v>
+        <v>448.2105280598465</v>
       </c>
       <c r="W28" t="n">
-        <v>547.0998432705837</v>
+        <v>541.8914463195239</v>
       </c>
       <c r="X28" t="n">
-        <v>619.9206342947773</v>
+        <v>614.7122373437174</v>
       </c>
       <c r="Y28" t="n">
-        <v>653.1199349738096</v>
+        <v>647.9115380227497</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>597.4524900262056</v>
+        <v>593.4524900262663</v>
       </c>
       <c r="C29" t="n">
-        <v>467.6801887706562</v>
+        <v>463.6801887707169</v>
       </c>
       <c r="D29" t="n">
-        <v>377.4386173162624</v>
+        <v>373.4386173163231</v>
       </c>
       <c r="E29" t="n">
-        <v>293.2332742790214</v>
+        <v>289.2332742790821</v>
       </c>
       <c r="F29" t="n">
-        <v>208.4962755840599</v>
+        <v>204.4962755841206</v>
       </c>
       <c r="G29" t="n">
-        <v>126.3120357733081</v>
+        <v>122.3120357733687</v>
       </c>
       <c r="H29" t="n">
-        <v>52.85408398404886</v>
+        <v>51.8400000000007</v>
       </c>
       <c r="I29" t="n">
-        <v>51.92</v>
+        <v>51.8400000000007</v>
       </c>
       <c r="J29" t="n">
-        <v>134.440205073642</v>
+        <v>134.3602050736427</v>
       </c>
       <c r="K29" t="n">
-        <v>776.950205073642</v>
+        <v>310.0317798977633</v>
       </c>
       <c r="L29" t="n">
-        <v>994.8863275862049</v>
+        <v>951.5517798977719</v>
       </c>
       <c r="M29" t="n">
-        <v>1637.396327586205</v>
+        <v>1001.294971748401</v>
       </c>
       <c r="N29" t="n">
-        <v>1646.814971748371</v>
+        <v>1642.814971748406</v>
       </c>
       <c r="O29" t="n">
-        <v>1809.956778005698</v>
+        <v>1805.956778005733</v>
       </c>
       <c r="P29" t="n">
-        <v>2008.265727912157</v>
+        <v>2004.265727912192</v>
       </c>
       <c r="Q29" t="n">
-        <v>2596</v>
+        <v>2592.000000000035</v>
       </c>
       <c r="R29" t="n">
-        <v>2596</v>
+        <v>2592.00000000006</v>
       </c>
       <c r="S29" t="n">
-        <v>2452.504870855986</v>
+        <v>2448.504870856046</v>
       </c>
       <c r="T29" t="n">
-        <v>2190.313881748914</v>
+        <v>2186.313881748974</v>
       </c>
       <c r="U29" t="n">
-        <v>1858.889943810872</v>
+        <v>1854.889943810933</v>
       </c>
       <c r="V29" t="n">
-        <v>1546.919212329232</v>
+        <v>1542.919212329293</v>
       </c>
       <c r="W29" t="n">
-        <v>1226.339943661608</v>
+        <v>1222.339943661669</v>
       </c>
       <c r="X29" t="n">
-        <v>952.3178896609338</v>
+        <v>948.3178896609945</v>
       </c>
       <c r="Y29" t="n">
-        <v>760.0780586682001</v>
+        <v>756.0780586682608</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>599.0444115421303</v>
+        <v>1326.040017598838</v>
       </c>
       <c r="C30" t="n">
-        <v>558.5394494759493</v>
+        <v>1100.525695149684</v>
       </c>
       <c r="D30" t="n">
-        <v>531.3296647307951</v>
+        <v>749.073486162105</v>
       </c>
       <c r="E30" t="n">
-        <v>185.1962331935096</v>
+        <v>402.9400546248195</v>
       </c>
       <c r="F30" t="n">
-        <v>59.95314317241791</v>
+        <v>59.87314317241864</v>
       </c>
       <c r="G30" t="n">
-        <v>55.91964972137067</v>
+        <v>55.83964972137139</v>
       </c>
       <c r="H30" t="n">
-        <v>51.92</v>
+        <v>51.8400000000007</v>
       </c>
       <c r="I30" t="n">
-        <v>51.92</v>
+        <v>51.8400000000007</v>
       </c>
       <c r="J30" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036016</v>
       </c>
       <c r="K30" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149661</v>
       </c>
       <c r="L30" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573361</v>
       </c>
       <c r="M30" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N30" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.671284215311</v>
       </c>
       <c r="O30" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672615</v>
       </c>
       <c r="P30" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>2174.638747796677</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R30" t="n">
-        <v>1992.888314091777</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S30" t="n">
-        <v>1859.857639456283</v>
+        <v>1938.368397028142</v>
       </c>
       <c r="T30" t="n">
-        <v>1777.686588255059</v>
+        <v>1856.197345826918</v>
       </c>
       <c r="U30" t="n">
-        <v>1697.725723622128</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V30" t="n">
-        <v>1603.270504236754</v>
+        <v>1681.781261808612</v>
       </c>
       <c r="W30" t="n">
-        <v>1490.772380085412</v>
+        <v>1569.283137657271</v>
       </c>
       <c r="X30" t="n">
-        <v>1066.668602867848</v>
+        <v>1469.421784682132</v>
       </c>
       <c r="Y30" t="n">
-        <v>987.4853778515511</v>
+        <v>1390.238559665834</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>681.5388756890411</v>
+        <v>681.4588756890419</v>
       </c>
       <c r="C31" t="n">
-        <v>729.3308815074769</v>
+        <v>729.2508815074776</v>
       </c>
       <c r="D31" t="n">
-        <v>764.4400256324769</v>
+        <v>764.3600256324777</v>
       </c>
       <c r="E31" t="n">
-        <v>804.0589298438899</v>
+        <v>803.9789298438907</v>
       </c>
       <c r="F31" t="n">
-        <v>850.2099024358254</v>
+        <v>850.1299024358261</v>
       </c>
       <c r="G31" t="n">
-        <v>926.0259486505795</v>
+        <v>925.9459486505802</v>
       </c>
       <c r="H31" t="n">
-        <v>1022.840277088666</v>
+        <v>1022.760277088666</v>
       </c>
       <c r="I31" t="n">
-        <v>1184.392618975568</v>
+        <v>1184.312618975569</v>
       </c>
       <c r="J31" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K31" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564889</v>
       </c>
       <c r="L31" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221214</v>
       </c>
       <c r="M31" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499645</v>
       </c>
       <c r="N31" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241609</v>
       </c>
       <c r="O31" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P31" t="n">
-        <v>819.9781109568783</v>
+        <v>819.898110956879</v>
       </c>
       <c r="Q31" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380931</v>
       </c>
       <c r="R31" t="n">
-        <v>82.69634147829413</v>
+        <v>82.61634147829481</v>
       </c>
       <c r="S31" t="n">
-        <v>51.92</v>
+        <v>51.8400000000007</v>
       </c>
       <c r="T31" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506088</v>
       </c>
       <c r="U31" t="n">
-        <v>327.6791351738997</v>
+        <v>332.727532124961</v>
       </c>
       <c r="V31" t="n">
-        <v>448.2905280598457</v>
+        <v>453.338925010907</v>
       </c>
       <c r="W31" t="n">
-        <v>541.9714463195231</v>
+        <v>547.0198432705845</v>
       </c>
       <c r="X31" t="n">
-        <v>614.7922373437167</v>
+        <v>619.8406342947781</v>
       </c>
       <c r="Y31" t="n">
-        <v>647.991538022749</v>
+        <v>647.9115380227497</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.4524900262056</v>
+        <v>596.4384060421575</v>
       </c>
       <c r="C32" t="n">
-        <v>467.6801887706562</v>
+        <v>466.666104786608</v>
       </c>
       <c r="D32" t="n">
-        <v>377.4386173162624</v>
+        <v>376.4245333322143</v>
       </c>
       <c r="E32" t="n">
-        <v>293.2332742790214</v>
+        <v>292.2191902949732</v>
       </c>
       <c r="F32" t="n">
-        <v>208.4962755840599</v>
+        <v>207.4821916000117</v>
       </c>
       <c r="G32" t="n">
-        <v>126.3120357733081</v>
+        <v>125.2979517892599</v>
       </c>
       <c r="H32" t="n">
-        <v>51.92</v>
+        <v>51.8400000000007</v>
       </c>
       <c r="I32" t="n">
-        <v>51.92</v>
+        <v>51.8400000000007</v>
       </c>
       <c r="J32" t="n">
-        <v>134.440205073642</v>
+        <v>560.3618942939378</v>
       </c>
       <c r="K32" t="n">
-        <v>776.950205073642</v>
+        <v>736.0334691180584</v>
       </c>
       <c r="L32" t="n">
-        <v>1419.460205073642</v>
+        <v>1001.294971748382</v>
       </c>
       <c r="M32" t="n">
-        <v>2061.970205073642</v>
+        <v>1001.294971748382</v>
       </c>
       <c r="N32" t="n">
-        <v>2234.549243836214</v>
+        <v>1642.814971748384</v>
       </c>
       <c r="O32" t="n">
-        <v>2397.691050093541</v>
+        <v>1805.956778005711</v>
       </c>
       <c r="P32" t="n">
-        <v>2596</v>
+        <v>2004.26572791217</v>
       </c>
       <c r="Q32" t="n">
-        <v>2596</v>
+        <v>2592.000000000013</v>
       </c>
       <c r="R32" t="n">
-        <v>2596</v>
+        <v>2592.000000000035</v>
       </c>
       <c r="S32" t="n">
-        <v>2452.504870855986</v>
+        <v>2448.504870856021</v>
       </c>
       <c r="T32" t="n">
-        <v>2190.313881748914</v>
+        <v>2186.313881748949</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.889943810872</v>
+        <v>1857.875859826824</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.919212329232</v>
+        <v>1545.905128345184</v>
       </c>
       <c r="W32" t="n">
-        <v>1226.339943661608</v>
+        <v>1225.32585967756</v>
       </c>
       <c r="X32" t="n">
-        <v>952.3178896609338</v>
+        <v>951.3038056768858</v>
       </c>
       <c r="Y32" t="n">
-        <v>760.0780586682001</v>
+        <v>759.063974684152</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1247.529260026979</v>
+        <v>1326.040017598838</v>
       </c>
       <c r="C33" t="n">
-        <v>1100.605695149683</v>
+        <v>1100.525695149684</v>
       </c>
       <c r="D33" t="n">
-        <v>749.1534861621044</v>
+        <v>749.073486162105</v>
       </c>
       <c r="E33" t="n">
-        <v>403.0200546248188</v>
+        <v>402.9400546248195</v>
       </c>
       <c r="F33" t="n">
-        <v>59.95314317241791</v>
+        <v>59.87314317241861</v>
       </c>
       <c r="G33" t="n">
-        <v>55.91964972137067</v>
+        <v>55.83964972137137</v>
       </c>
       <c r="H33" t="n">
-        <v>51.92</v>
+        <v>51.8400000000007</v>
       </c>
       <c r="I33" t="n">
-        <v>51.92</v>
+        <v>51.8400000000007</v>
       </c>
       <c r="J33" t="n">
-        <v>245.6876497036009</v>
+        <v>245.6076497036016</v>
       </c>
       <c r="K33" t="n">
-        <v>554.1988055149654</v>
+        <v>554.1188055149661</v>
       </c>
       <c r="L33" t="n">
-        <v>985.9874996573354</v>
+        <v>985.9074996573361</v>
       </c>
       <c r="M33" t="n">
-        <v>1259.291891400195</v>
+        <v>1259.211891400195</v>
       </c>
       <c r="N33" t="n">
-        <v>1584.75128421531</v>
+        <v>1584.671284215311</v>
       </c>
       <c r="O33" t="n">
-        <v>1999.600074672614</v>
+        <v>1999.520074672615</v>
       </c>
       <c r="P33" t="n">
-        <v>2253.229505368536</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>2174.638747796677</v>
+        <v>2253.149505368536</v>
       </c>
       <c r="R33" t="n">
-        <v>1992.888314091777</v>
+        <v>2071.399071663636</v>
       </c>
       <c r="S33" t="n">
-        <v>1859.857639456283</v>
+        <v>1938.368397028142</v>
       </c>
       <c r="T33" t="n">
-        <v>1777.686588255059</v>
+        <v>1856.197345826918</v>
       </c>
       <c r="U33" t="n">
-        <v>1697.725723622128</v>
+        <v>1776.236481193986</v>
       </c>
       <c r="V33" t="n">
-        <v>1603.270504236754</v>
+        <v>1681.781261808612</v>
       </c>
       <c r="W33" t="n">
-        <v>1490.772380085412</v>
+        <v>1569.283137657271</v>
       </c>
       <c r="X33" t="n">
-        <v>1390.911027110273</v>
+        <v>1469.421784682132</v>
       </c>
       <c r="Y33" t="n">
-        <v>1311.727802093975</v>
+        <v>1390.238559665834</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>686.6672726401017</v>
+        <v>686.5872726401025</v>
       </c>
       <c r="C34" t="n">
-        <v>734.4592784585375</v>
+        <v>734.3792784585382</v>
       </c>
       <c r="D34" t="n">
-        <v>769.5684225835375</v>
+        <v>769.4884225835383</v>
       </c>
       <c r="E34" t="n">
-        <v>809.1873267949505</v>
+        <v>809.1073267949513</v>
       </c>
       <c r="F34" t="n">
-        <v>855.338299386886</v>
+        <v>855.2582993868867</v>
       </c>
       <c r="G34" t="n">
-        <v>926.0259486505795</v>
+        <v>931.0743456016409</v>
       </c>
       <c r="H34" t="n">
-        <v>1022.840277088666</v>
+        <v>1027.888674039727</v>
       </c>
       <c r="I34" t="n">
-        <v>1184.392618975568</v>
+        <v>1189.441015926629</v>
       </c>
       <c r="J34" t="n">
-        <v>1511.063618808347</v>
+        <v>1510.983618808348</v>
       </c>
       <c r="K34" t="n">
-        <v>1615.190403564888</v>
+        <v>1615.110403564889</v>
       </c>
       <c r="L34" t="n">
-        <v>1605.576770221213</v>
+        <v>1605.496770221214</v>
       </c>
       <c r="M34" t="n">
-        <v>1503.006687499644</v>
+        <v>1502.926687499645</v>
       </c>
       <c r="N34" t="n">
-        <v>1347.016646241608</v>
+        <v>1346.936646241609</v>
       </c>
       <c r="O34" t="n">
-        <v>1113.682925280855</v>
+        <v>1113.602925280855</v>
       </c>
       <c r="P34" t="n">
-        <v>819.9781109568783</v>
+        <v>819.8981109568789</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.9758216380924</v>
+        <v>463.8958216380931</v>
       </c>
       <c r="R34" t="n">
-        <v>82.69634147829413</v>
+        <v>82.61634147829483</v>
       </c>
       <c r="S34" t="n">
-        <v>51.92</v>
+        <v>51.8400000000007</v>
       </c>
       <c r="T34" t="n">
-        <v>164.4325496506081</v>
+        <v>164.3525496506088</v>
       </c>
       <c r="U34" t="n">
-        <v>332.8075321249603</v>
+        <v>332.727532124961</v>
       </c>
       <c r="V34" t="n">
-        <v>453.4189250109063</v>
+        <v>453.338925010907</v>
       </c>
       <c r="W34" t="n">
-        <v>547.0998432705837</v>
+        <v>547.0198432705845</v>
       </c>
       <c r="X34" t="n">
-        <v>619.9206342947773</v>
+        <v>619.8406342947781</v>
       </c>
       <c r="Y34" t="n">
-        <v>653.1199349738096</v>
+        <v>653.0399349738103</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>443.3918839655994</v>
+        <v>439.3918839656653</v>
       </c>
       <c r="C35" t="n">
-        <v>337.8620069524742</v>
+        <v>333.8620069525401</v>
       </c>
       <c r="D35" t="n">
-        <v>271.8628597405047</v>
+        <v>267.8628597405706</v>
       </c>
       <c r="E35" t="n">
-        <v>211.8999409456879</v>
+        <v>207.8999409457538</v>
       </c>
       <c r="F35" t="n">
-        <v>151.4053664931506</v>
+        <v>147.4053664932166</v>
       </c>
       <c r="G35" t="n">
-        <v>94.17552754683496</v>
+        <v>94.095527546836</v>
       </c>
       <c r="H35" t="n">
-        <v>44.96</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="I35" t="n">
-        <v>44.96</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="J35" t="n">
-        <v>127.480205073642</v>
+        <v>127.400205073643</v>
       </c>
       <c r="K35" t="n">
-        <v>303.1517798977626</v>
+        <v>303.0717798977637</v>
       </c>
       <c r="L35" t="n">
-        <v>521.0879024103255</v>
+        <v>771.7692438362908</v>
       </c>
       <c r="M35" t="n">
-        <v>1077.467902410326</v>
+        <v>1327.159243836293</v>
       </c>
       <c r="N35" t="n">
-        <v>1633.847902410326</v>
+        <v>1882.549243836295</v>
       </c>
       <c r="O35" t="n">
-        <v>1796.989708667653</v>
+        <v>2045.691050093621</v>
       </c>
       <c r="P35" t="n">
-        <v>1995.298658574112</v>
+        <v>2244.00000000008</v>
       </c>
       <c r="Q35" t="n">
-        <v>2248</v>
+        <v>2244.00000000008</v>
       </c>
       <c r="R35" t="n">
-        <v>2248</v>
+        <v>2244.000000000066</v>
       </c>
       <c r="S35" t="n">
-        <v>2128.74729509841</v>
+        <v>2124.747295098476</v>
       </c>
       <c r="T35" t="n">
-        <v>1890.798730233762</v>
+        <v>1886.798730233828</v>
       </c>
       <c r="U35" t="n">
-        <v>1583.617216538145</v>
+        <v>1579.617216538211</v>
       </c>
       <c r="V35" t="n">
-        <v>1295.888909298929</v>
+        <v>1291.888909298995</v>
       </c>
       <c r="W35" t="n">
-        <v>999.5520648737293</v>
+        <v>995.5520648737952</v>
       </c>
       <c r="X35" t="n">
-        <v>749.7724351154791</v>
+        <v>745.772435115545</v>
       </c>
       <c r="Y35" t="n">
-        <v>581.7750283651696</v>
+        <v>577.7750283652356</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>840.3721388109582</v>
+        <v>1186.587481927337</v>
       </c>
       <c r="C36" t="n">
-        <v>475.6247525023528</v>
+        <v>1170.32494410358</v>
       </c>
       <c r="D36" t="n">
-        <v>472.6573919996229</v>
+        <v>818.8727351160016</v>
       </c>
       <c r="E36" t="n">
-        <v>126.5239604623374</v>
+        <v>472.7393035787161</v>
       </c>
       <c r="F36" t="n">
-        <v>126.5239604623374</v>
+        <v>129.6723921263152</v>
       </c>
       <c r="G36" t="n">
-        <v>126.5239604623374</v>
+        <v>129.6723921263152</v>
       </c>
       <c r="H36" t="n">
-        <v>126.5239604623374</v>
+        <v>129.6723921263152</v>
       </c>
       <c r="I36" t="n">
-        <v>44.96</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="J36" t="n">
-        <v>238.7276497036009</v>
+        <v>238.6476497036019</v>
       </c>
       <c r="K36" t="n">
-        <v>547.2388055149654</v>
+        <v>547.1588055149664</v>
       </c>
       <c r="L36" t="n">
-        <v>979.0274996573354</v>
+        <v>978.9474996573364</v>
       </c>
       <c r="M36" t="n">
-        <v>1252.331891400195</v>
+        <v>1252.251891400196</v>
       </c>
       <c r="N36" t="n">
-        <v>1577.79128421531</v>
+        <v>1577.711284215311</v>
       </c>
       <c r="O36" t="n">
-        <v>1992.640074672614</v>
+        <v>1990.370569304144</v>
       </c>
       <c r="P36" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000066</v>
       </c>
       <c r="Q36" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000066</v>
       </c>
       <c r="R36" t="n">
-        <v>2088.76149590606</v>
+        <v>2086.49199053759</v>
       </c>
       <c r="S36" t="n">
-        <v>1979.973245512989</v>
+        <v>1977.70374014452</v>
       </c>
       <c r="T36" t="n">
-        <v>1922.04461855419</v>
+        <v>1919.77511318572</v>
       </c>
       <c r="U36" t="n">
-        <v>1866.326178163683</v>
+        <v>1864.056672795213</v>
       </c>
       <c r="V36" t="n">
-        <v>1796.113383020733</v>
+        <v>1793.843877652263</v>
       </c>
       <c r="W36" t="n">
-        <v>1707.857683111815</v>
+        <v>1705.588177743346</v>
       </c>
       <c r="X36" t="n">
-        <v>1283.753905894252</v>
+        <v>1629.969249010631</v>
       </c>
       <c r="Y36" t="n">
-        <v>1228.813105120379</v>
+        <v>1575.028448236758</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>728.5863543804243</v>
+        <v>845.9472726401027</v>
       </c>
       <c r="C37" t="n">
-        <v>800.13836019886</v>
+        <v>917.4992784585385</v>
       </c>
       <c r="D37" t="n">
-        <v>859.0075043238601</v>
+        <v>976.3684225835385</v>
       </c>
       <c r="E37" t="n">
-        <v>922.3864085352731</v>
+        <v>1039.747326794952</v>
       </c>
       <c r="F37" t="n">
-        <v>971.9276676500707</v>
+        <v>1109.658299386887</v>
       </c>
       <c r="G37" t="n">
-        <v>971.9276676500707</v>
+        <v>1109.658299386887</v>
       </c>
       <c r="H37" t="n">
-        <v>1092.501996088157</v>
+        <v>1109.658299386887</v>
       </c>
       <c r="I37" t="n">
-        <v>1277.814337975059</v>
+        <v>1294.97064127379</v>
       </c>
       <c r="J37" t="n">
-        <v>1286.695337807839</v>
+        <v>1428.839800524244</v>
       </c>
       <c r="K37" t="n">
-        <v>1414.582122564379</v>
+        <v>1428.839800524244</v>
       </c>
       <c r="L37" t="n">
-        <v>1428.919800524243</v>
+        <v>1428.839800524244</v>
       </c>
       <c r="M37" t="n">
-        <v>1350.592142045098</v>
+        <v>1350.512142045099</v>
       </c>
       <c r="N37" t="n">
-        <v>1218.844525029487</v>
+        <v>1218.764525029488</v>
       </c>
       <c r="O37" t="n">
-        <v>1009.753228311157</v>
+        <v>1009.673228311158</v>
       </c>
       <c r="P37" t="n">
-        <v>740.2908382296055</v>
+        <v>740.2108382296065</v>
       </c>
       <c r="Q37" t="n">
-        <v>408.5309731532439</v>
+        <v>408.4509731532449</v>
       </c>
       <c r="R37" t="n">
-        <v>51.49391723586989</v>
+        <v>51.4139172358709</v>
       </c>
       <c r="S37" t="n">
-        <v>44.96</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="T37" t="n">
-        <v>181.2325496506081</v>
+        <v>181.1525496506092</v>
       </c>
       <c r="U37" t="n">
-        <v>373.3675321249603</v>
+        <v>373.2875321249614</v>
       </c>
       <c r="V37" t="n">
-        <v>517.7389250109063</v>
+        <v>517.6589250109073</v>
       </c>
       <c r="W37" t="n">
-        <v>517.7389250109063</v>
+        <v>635.0998432705848</v>
       </c>
       <c r="X37" t="n">
-        <v>614.3197160350999</v>
+        <v>731.6806342947783</v>
       </c>
       <c r="Y37" t="n">
-        <v>671.2790167141321</v>
+        <v>788.6399349738106</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>443.3918839656435</v>
+        <v>444.0238605876124</v>
       </c>
       <c r="C38" t="n">
-        <v>337.8620069525183</v>
+        <v>338.4939835744872</v>
       </c>
       <c r="D38" t="n">
-        <v>271.8628597405488</v>
+        <v>272.4948363625177</v>
       </c>
       <c r="E38" t="n">
-        <v>211.899940945732</v>
+        <v>212.5319175677008</v>
       </c>
       <c r="F38" t="n">
-        <v>151.4053664931947</v>
+        <v>152.0373431151636</v>
       </c>
       <c r="G38" t="n">
-        <v>93.46355092486712</v>
+        <v>94.095527546836</v>
       </c>
       <c r="H38" t="n">
-        <v>44.96</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="I38" t="n">
-        <v>44.96</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="J38" t="n">
-        <v>553.4818942939371</v>
+        <v>553.4018942939382</v>
       </c>
       <c r="K38" t="n">
-        <v>729.1534691180577</v>
+        <v>1108.791894293951</v>
       </c>
       <c r="L38" t="n">
-        <v>947.0895916306206</v>
+        <v>1326.728016806514</v>
       </c>
       <c r="M38" t="n">
-        <v>1330.169243836214</v>
+        <v>1882.118016806516</v>
       </c>
       <c r="N38" t="n">
-        <v>1330.169243836214</v>
+        <v>1882.549243836266</v>
       </c>
       <c r="O38" t="n">
-        <v>1493.311050093541</v>
+        <v>2045.691050093592</v>
       </c>
       <c r="P38" t="n">
-        <v>1691.62</v>
+        <v>2244.000000000051</v>
       </c>
       <c r="Q38" t="n">
-        <v>2248</v>
+        <v>2244.000000000051</v>
       </c>
       <c r="R38" t="n">
-        <v>2248.000000000044</v>
+        <v>2244.000000000051</v>
       </c>
       <c r="S38" t="n">
-        <v>2128.747295098454</v>
+        <v>2124.747295098461</v>
       </c>
       <c r="T38" t="n">
-        <v>1890.798730233806</v>
+        <v>1886.798730233814</v>
       </c>
       <c r="U38" t="n">
-        <v>1583.617216538189</v>
+        <v>1579.617216538196</v>
       </c>
       <c r="V38" t="n">
-        <v>1295.888909298973</v>
+        <v>1291.88890929898</v>
       </c>
       <c r="W38" t="n">
-        <v>999.5520648737734</v>
+        <v>995.5520648737806</v>
       </c>
       <c r="X38" t="n">
-        <v>749.7724351155232</v>
+        <v>745.7724351155305</v>
       </c>
       <c r="Y38" t="n">
-        <v>581.7750283652138</v>
+        <v>582.4070049871826</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1458.751078208797</v>
+        <v>1107.996724355464</v>
       </c>
       <c r="C39" t="n">
-        <v>1094.003691900192</v>
+        <v>1091.734186531707</v>
       </c>
       <c r="D39" t="n">
-        <v>742.5514829126132</v>
+        <v>740.2819775441289</v>
       </c>
       <c r="E39" t="n">
-        <v>396.4180513753277</v>
+        <v>394.1485460068434</v>
       </c>
       <c r="F39" t="n">
-        <v>53.35113992292679</v>
+        <v>394.1485460068434</v>
       </c>
       <c r="G39" t="n">
-        <v>53.35113992292679</v>
+        <v>394.1485460068434</v>
       </c>
       <c r="H39" t="n">
-        <v>53.35113992292679</v>
+        <v>65.9064720430485</v>
       </c>
       <c r="I39" t="n">
-        <v>44.96</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="J39" t="n">
-        <v>238.7276497036009</v>
+        <v>238.6476497036019</v>
       </c>
       <c r="K39" t="n">
-        <v>547.2388055149654</v>
+        <v>547.1588055149664</v>
       </c>
       <c r="L39" t="n">
-        <v>979.0274996573354</v>
+        <v>978.9474996573364</v>
       </c>
       <c r="M39" t="n">
-        <v>1252.331891400195</v>
+        <v>1252.251891400196</v>
       </c>
       <c r="N39" t="n">
-        <v>1577.79128421531</v>
+        <v>1575.521778846826</v>
       </c>
       <c r="O39" t="n">
-        <v>1992.640074672614</v>
+        <v>1990.37056930413</v>
       </c>
       <c r="P39" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000051</v>
       </c>
       <c r="Q39" t="n">
-        <v>2167.678747796677</v>
+        <v>2165.409242428193</v>
       </c>
       <c r="R39" t="n">
-        <v>2010.170738334202</v>
+        <v>2007.901232965717</v>
       </c>
       <c r="S39" t="n">
-        <v>1901.382487941131</v>
+        <v>1550.628134087799</v>
       </c>
       <c r="T39" t="n">
-        <v>1843.453860982331</v>
+        <v>1492.699507128999</v>
       </c>
       <c r="U39" t="n">
-        <v>1787.735420591825</v>
+        <v>1436.981066738492</v>
       </c>
       <c r="V39" t="n">
-        <v>1717.522625448875</v>
+        <v>1366.768271595542</v>
       </c>
       <c r="W39" t="n">
-        <v>1629.266925539957</v>
+        <v>1278.512571686624</v>
       </c>
       <c r="X39" t="n">
-        <v>1553.647996807242</v>
+        <v>1202.89364295391</v>
       </c>
       <c r="Y39" t="n">
-        <v>1498.707196033369</v>
+        <v>1147.952842180037</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>728.5863543804243</v>
+        <v>667.4297388135333</v>
       </c>
       <c r="C40" t="n">
-        <v>800.13836019886</v>
+        <v>738.981744631969</v>
       </c>
       <c r="D40" t="n">
-        <v>859.0075043238601</v>
+        <v>738.981744631969</v>
       </c>
       <c r="E40" t="n">
-        <v>922.3864085352731</v>
+        <v>802.360648843382</v>
       </c>
       <c r="F40" t="n">
-        <v>992.2973811272087</v>
+        <v>872.2716214353176</v>
       </c>
       <c r="G40" t="n">
-        <v>1091.873427341963</v>
+        <v>971.8476676500717</v>
       </c>
       <c r="H40" t="n">
-        <v>1092.501996088157</v>
+        <v>1092.421996088158</v>
       </c>
       <c r="I40" t="n">
-        <v>1277.814337975059</v>
+        <v>1277.73433797506</v>
       </c>
       <c r="J40" t="n">
-        <v>1286.695337807839</v>
+        <v>1286.61533780784</v>
       </c>
       <c r="K40" t="n">
-        <v>1414.582122564379</v>
+        <v>1414.50212256438</v>
       </c>
       <c r="L40" t="n">
-        <v>1428.919800524243</v>
+        <v>1428.839800524244</v>
       </c>
       <c r="M40" t="n">
-        <v>1350.592142045098</v>
+        <v>1350.512142045099</v>
       </c>
       <c r="N40" t="n">
-        <v>1218.844525029487</v>
+        <v>1218.764525029488</v>
       </c>
       <c r="O40" t="n">
-        <v>1009.753228311157</v>
+        <v>1009.673228311158</v>
       </c>
       <c r="P40" t="n">
-        <v>740.2908382296055</v>
+        <v>740.2108382296065</v>
       </c>
       <c r="Q40" t="n">
-        <v>408.5309731532438</v>
+        <v>408.4509731532449</v>
       </c>
       <c r="R40" t="n">
-        <v>51.49391723586987</v>
+        <v>51.4139172358709</v>
       </c>
       <c r="S40" t="n">
-        <v>44.96</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="T40" t="n">
-        <v>181.2325496506081</v>
+        <v>147.0064087099857</v>
       </c>
       <c r="U40" t="n">
-        <v>373.3675321249603</v>
+        <v>339.141391184338</v>
       </c>
       <c r="V40" t="n">
-        <v>517.7389250109063</v>
+        <v>339.141391184338</v>
       </c>
       <c r="W40" t="n">
-        <v>517.7389250109063</v>
+        <v>456.5823094440154</v>
       </c>
       <c r="X40" t="n">
-        <v>614.3197160350999</v>
+        <v>553.1631004682089</v>
       </c>
       <c r="Y40" t="n">
-        <v>671.2790167141321</v>
+        <v>610.1224011472411</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>444.1038605876113</v>
+        <v>444.0238605876124</v>
       </c>
       <c r="C41" t="n">
-        <v>338.5739835744861</v>
+        <v>338.4939835744872</v>
       </c>
       <c r="D41" t="n">
-        <v>272.5748363625166</v>
+        <v>272.4948363625177</v>
       </c>
       <c r="E41" t="n">
-        <v>212.6119175676998</v>
+        <v>212.5319175677008</v>
       </c>
       <c r="F41" t="n">
-        <v>152.1173431151626</v>
+        <v>152.0373431151636</v>
       </c>
       <c r="G41" t="n">
-        <v>94.17552754683497</v>
+        <v>94.095527546836</v>
       </c>
       <c r="H41" t="n">
-        <v>44.96</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="I41" t="n">
-        <v>44.96</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="J41" t="n">
-        <v>127.480205073642</v>
+        <v>127.400205073643</v>
       </c>
       <c r="K41" t="n">
-        <v>303.1517798977626</v>
+        <v>682.7902050736558</v>
       </c>
       <c r="L41" t="n">
-        <v>859.5317798977626</v>
+        <v>900.7263275862186</v>
       </c>
       <c r="M41" t="n">
-        <v>1330.169243836214</v>
+        <v>1456.116327586219</v>
       </c>
       <c r="N41" t="n">
-        <v>1886.549243836214</v>
+        <v>1882.549243836266</v>
       </c>
       <c r="O41" t="n">
-        <v>2049.691050093541</v>
+        <v>2045.691050093592</v>
       </c>
       <c r="P41" t="n">
-        <v>2248</v>
+        <v>2244.000000000051</v>
       </c>
       <c r="Q41" t="n">
-        <v>2248</v>
+        <v>2244.000000000051</v>
       </c>
       <c r="R41" t="n">
-        <v>2248</v>
+        <v>2244.000000000051</v>
       </c>
       <c r="S41" t="n">
-        <v>2129.459271720421</v>
+        <v>2124.747295098461</v>
       </c>
       <c r="T41" t="n">
-        <v>1891.510706855774</v>
+        <v>1886.798730233814</v>
       </c>
       <c r="U41" t="n">
-        <v>1584.329193160157</v>
+        <v>1579.617216538196</v>
       </c>
       <c r="V41" t="n">
-        <v>1296.600885920941</v>
+        <v>1291.88890929898</v>
       </c>
       <c r="W41" t="n">
-        <v>1000.264041495741</v>
+        <v>995.5520648737806</v>
       </c>
       <c r="X41" t="n">
-        <v>750.484411737491</v>
+        <v>745.7724351155305</v>
       </c>
       <c r="Y41" t="n">
-        <v>582.4870049871815</v>
+        <v>577.775028365221</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>257.5522663890268</v>
+        <v>1107.996724355457</v>
       </c>
       <c r="C42" t="n">
-        <v>241.2897285652699</v>
+        <v>1091.7341865317</v>
       </c>
       <c r="D42" t="n">
-        <v>238.32236806254</v>
+        <v>740.2819775441217</v>
       </c>
       <c r="E42" t="n">
-        <v>238.32236806254</v>
+        <v>394.1485460068362</v>
       </c>
       <c r="F42" t="n">
-        <v>238.32236806254</v>
+        <v>51.08163455443525</v>
       </c>
       <c r="G42" t="n">
-        <v>238.32236806254</v>
+        <v>51.08163455443525</v>
       </c>
       <c r="H42" t="n">
-        <v>238.32236806254</v>
+        <v>51.08163455443525</v>
       </c>
       <c r="I42" t="n">
-        <v>44.96</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="J42" t="n">
-        <v>238.7276497036009</v>
+        <v>238.6476497036019</v>
       </c>
       <c r="K42" t="n">
-        <v>547.2388055149654</v>
+        <v>547.1588055149664</v>
       </c>
       <c r="L42" t="n">
-        <v>979.0274996573354</v>
+        <v>978.9474996573364</v>
       </c>
       <c r="M42" t="n">
-        <v>1252.331891400195</v>
+        <v>1252.251891400196</v>
       </c>
       <c r="N42" t="n">
-        <v>1577.79128421531</v>
+        <v>1577.711284215311</v>
       </c>
       <c r="O42" t="n">
-        <v>1992.640074672614</v>
+        <v>1990.370569304122</v>
       </c>
       <c r="P42" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000044</v>
       </c>
       <c r="Q42" t="n">
-        <v>2167.678747796677</v>
+        <v>2165.409242428186</v>
       </c>
       <c r="R42" t="n">
-        <v>2010.170738334202</v>
+        <v>2007.90123296571</v>
       </c>
       <c r="S42" t="n">
-        <v>1901.382487941131</v>
+        <v>1899.11298257264</v>
       </c>
       <c r="T42" t="n">
-        <v>1843.453860982331</v>
+        <v>1492.699507128991</v>
       </c>
       <c r="U42" t="n">
-        <v>1787.735420591825</v>
+        <v>1436.981066738485</v>
       </c>
       <c r="V42" t="n">
-        <v>1369.037776964026</v>
+        <v>1366.768271595535</v>
       </c>
       <c r="W42" t="n">
-        <v>932.2972285702601</v>
+        <v>1278.512571686617</v>
       </c>
       <c r="X42" t="n">
-        <v>508.1934513526969</v>
+        <v>1202.893642953902</v>
       </c>
       <c r="Y42" t="n">
-        <v>297.5083842135991</v>
+        <v>1147.952842180029</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>731.7606342947773</v>
+        <v>709.6747229894945</v>
       </c>
       <c r="C43" t="n">
-        <v>731.7606342947773</v>
+        <v>709.6747229894945</v>
       </c>
       <c r="D43" t="n">
-        <v>731.7606342947773</v>
+        <v>768.5438671144946</v>
       </c>
       <c r="E43" t="n">
-        <v>731.7606342947773</v>
+        <v>831.9227713259075</v>
       </c>
       <c r="F43" t="n">
-        <v>731.7606342947773</v>
+        <v>872.2716214353176</v>
       </c>
       <c r="G43" t="n">
-        <v>772.6021303664752</v>
+        <v>971.8476676500717</v>
       </c>
       <c r="H43" t="n">
-        <v>893.1764588045613</v>
+        <v>1092.421996088158</v>
       </c>
       <c r="I43" t="n">
-        <v>1078.488800691464</v>
+        <v>1277.73433797506</v>
       </c>
       <c r="J43" t="n">
-        <v>1428.919800524243</v>
+        <v>1286.61533780784</v>
       </c>
       <c r="K43" t="n">
-        <v>1428.919800524243</v>
+        <v>1414.50212256438</v>
       </c>
       <c r="L43" t="n">
-        <v>1428.919800524243</v>
+        <v>1428.839800524244</v>
       </c>
       <c r="M43" t="n">
-        <v>1350.592142045098</v>
+        <v>1350.512142045099</v>
       </c>
       <c r="N43" t="n">
-        <v>1218.844525029487</v>
+        <v>1218.764525029488</v>
       </c>
       <c r="O43" t="n">
-        <v>1009.753228311157</v>
+        <v>1009.673228311158</v>
       </c>
       <c r="P43" t="n">
-        <v>740.2908382296055</v>
+        <v>740.2108382296065</v>
       </c>
       <c r="Q43" t="n">
-        <v>408.5309731532438</v>
+        <v>408.4509731532449</v>
       </c>
       <c r="R43" t="n">
-        <v>51.49391723586987</v>
+        <v>51.4139172358709</v>
       </c>
       <c r="S43" t="n">
-        <v>44.96</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="T43" t="n">
-        <v>181.2325496506081</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="U43" t="n">
-        <v>373.3675321249603</v>
+        <v>237.0149824743532</v>
       </c>
       <c r="V43" t="n">
-        <v>517.7389250109063</v>
+        <v>381.3863753602992</v>
       </c>
       <c r="W43" t="n">
-        <v>635.1798432705838</v>
+        <v>498.8272936199766</v>
       </c>
       <c r="X43" t="n">
-        <v>731.7606342947773</v>
+        <v>595.4080846441701</v>
       </c>
       <c r="Y43" t="n">
-        <v>731.7606342947773</v>
+        <v>652.3673853232024</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>444.1038605876113</v>
+        <v>439.3918839656508</v>
       </c>
       <c r="C44" t="n">
-        <v>338.5739835744861</v>
+        <v>333.8620069525256</v>
       </c>
       <c r="D44" t="n">
-        <v>272.5748363625166</v>
+        <v>267.8628597405561</v>
       </c>
       <c r="E44" t="n">
-        <v>212.6119175676998</v>
+        <v>207.8999409457392</v>
       </c>
       <c r="F44" t="n">
-        <v>152.1173431151626</v>
+        <v>147.405366493202</v>
       </c>
       <c r="G44" t="n">
-        <v>94.17552754683496</v>
+        <v>94.09552754683598</v>
       </c>
       <c r="H44" t="n">
-        <v>44.96</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="I44" t="n">
-        <v>44.96</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="J44" t="n">
-        <v>553.4818942939371</v>
+        <v>553.4018942939382</v>
       </c>
       <c r="K44" t="n">
-        <v>729.1534691180577</v>
+        <v>729.0734691180588</v>
       </c>
       <c r="L44" t="n">
-        <v>947.0895916306206</v>
+        <v>947.0095916306217</v>
       </c>
       <c r="M44" t="n">
-        <v>1330.169243836214</v>
+        <v>947.0095916306218</v>
       </c>
       <c r="N44" t="n">
-        <v>1886.549243836214</v>
+        <v>1327.159243836264</v>
       </c>
       <c r="O44" t="n">
-        <v>2049.691050093541</v>
+        <v>1490.30105009359</v>
       </c>
       <c r="P44" t="n">
-        <v>2248</v>
+        <v>1688.610000000049</v>
       </c>
       <c r="Q44" t="n">
-        <v>2248</v>
+        <v>2244.000000000051</v>
       </c>
       <c r="R44" t="n">
-        <v>2248</v>
+        <v>2244.000000000051</v>
       </c>
       <c r="S44" t="n">
-        <v>2129.459271720422</v>
+        <v>2124.747295098461</v>
       </c>
       <c r="T44" t="n">
-        <v>1891.510706855774</v>
+        <v>1886.798730233814</v>
       </c>
       <c r="U44" t="n">
-        <v>1584.329193160157</v>
+        <v>1579.617216538196</v>
       </c>
       <c r="V44" t="n">
-        <v>1296.600885920941</v>
+        <v>1291.88890929898</v>
       </c>
       <c r="W44" t="n">
-        <v>1000.264041495741</v>
+        <v>995.5520648737806</v>
       </c>
       <c r="X44" t="n">
-        <v>750.484411737491</v>
+        <v>745.7724351155305</v>
       </c>
       <c r="Y44" t="n">
-        <v>582.4870049871815</v>
+        <v>577.775028365221</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1101.875089801022</v>
+        <v>489.6177849576254</v>
       </c>
       <c r="C45" t="n">
-        <v>1085.612551977265</v>
+        <v>473.3552471338685</v>
       </c>
       <c r="D45" t="n">
-        <v>734.1603429896863</v>
+        <v>470.3878866311385</v>
       </c>
       <c r="E45" t="n">
-        <v>388.0269114524009</v>
+        <v>470.3878866311385</v>
       </c>
       <c r="F45" t="n">
-        <v>44.96</v>
+        <v>470.3878866311385</v>
       </c>
       <c r="G45" t="n">
-        <v>44.96</v>
+        <v>142.111968937667</v>
       </c>
       <c r="H45" t="n">
-        <v>44.96</v>
+        <v>142.111968937667</v>
       </c>
       <c r="I45" t="n">
-        <v>44.96</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="J45" t="n">
-        <v>238.7276497036009</v>
+        <v>238.6476497036019</v>
       </c>
       <c r="K45" t="n">
-        <v>547.2388055149654</v>
+        <v>547.1588055149664</v>
       </c>
       <c r="L45" t="n">
-        <v>979.0274996573354</v>
+        <v>976.757994288851</v>
       </c>
       <c r="M45" t="n">
-        <v>1252.331891400195</v>
+        <v>1250.06238603171</v>
       </c>
       <c r="N45" t="n">
-        <v>1577.79128421531</v>
+        <v>1575.521778846826</v>
       </c>
       <c r="O45" t="n">
-        <v>1992.640074672614</v>
+        <v>1990.37056930413</v>
       </c>
       <c r="P45" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000051</v>
       </c>
       <c r="Q45" t="n">
-        <v>2246.269505368536</v>
+        <v>2244.000000000051</v>
       </c>
       <c r="R45" t="n">
-        <v>2088.76149590606</v>
+        <v>2086.491990537575</v>
       </c>
       <c r="S45" t="n">
-        <v>1979.973245512989</v>
+        <v>1977.703740144505</v>
       </c>
       <c r="T45" t="n">
-        <v>1922.04461855419</v>
+        <v>1919.775113185705</v>
       </c>
       <c r="U45" t="n">
-        <v>1866.326178163683</v>
+        <v>1864.056672795198</v>
       </c>
       <c r="V45" t="n">
-        <v>1796.113383020733</v>
+        <v>1793.843877652249</v>
       </c>
       <c r="W45" t="n">
-        <v>1620.87578561703</v>
+        <v>1357.103329258483</v>
       </c>
       <c r="X45" t="n">
-        <v>1545.256856884316</v>
+        <v>932.9995520409193</v>
       </c>
       <c r="Y45" t="n">
-        <v>1141.831207625594</v>
+        <v>529.5739027821977</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>789.0679719610695</v>
+        <v>845.9472726401027</v>
       </c>
       <c r="C46" t="n">
-        <v>789.0679719610695</v>
+        <v>917.4992784585385</v>
       </c>
       <c r="D46" t="n">
-        <v>847.9371160860695</v>
+        <v>976.3684225835385</v>
       </c>
       <c r="E46" t="n">
-        <v>911.3160202974825</v>
+        <v>1039.747326794952</v>
       </c>
       <c r="F46" t="n">
-        <v>981.2269928894179</v>
+        <v>1109.658299386887</v>
       </c>
       <c r="G46" t="n">
-        <v>1080.803039104172</v>
+        <v>1209.234345601641</v>
       </c>
       <c r="H46" t="n">
-        <v>1201.377367542258</v>
+        <v>1329.808674039727</v>
       </c>
       <c r="I46" t="n">
-        <v>1386.689709429161</v>
+        <v>1419.958800691465</v>
       </c>
       <c r="J46" t="n">
-        <v>1395.57070926194</v>
+        <v>1428.839800524244</v>
       </c>
       <c r="K46" t="n">
-        <v>1414.582122564379</v>
+        <v>1428.839800524244</v>
       </c>
       <c r="L46" t="n">
-        <v>1428.919800524243</v>
+        <v>1428.839800524244</v>
       </c>
       <c r="M46" t="n">
-        <v>1350.592142045098</v>
+        <v>1350.512142045099</v>
       </c>
       <c r="N46" t="n">
-        <v>1218.844525029487</v>
+        <v>1218.764525029488</v>
       </c>
       <c r="O46" t="n">
-        <v>1009.753228311157</v>
+        <v>1009.673228311158</v>
       </c>
       <c r="P46" t="n">
-        <v>740.2908382296055</v>
+        <v>740.2108382296065</v>
       </c>
       <c r="Q46" t="n">
-        <v>408.5309731532439</v>
+        <v>408.4509731532449</v>
       </c>
       <c r="R46" t="n">
-        <v>51.49391723586989</v>
+        <v>51.41391723587091</v>
       </c>
       <c r="S46" t="n">
-        <v>44.96</v>
+        <v>44.88000000000103</v>
       </c>
       <c r="T46" t="n">
-        <v>181.2325496506081</v>
+        <v>181.1525496506092</v>
       </c>
       <c r="U46" t="n">
-        <v>373.3675321249603</v>
+        <v>373.2875321249614</v>
       </c>
       <c r="V46" t="n">
-        <v>517.7389250109063</v>
+        <v>517.6589250109073</v>
       </c>
       <c r="W46" t="n">
-        <v>635.1798432705838</v>
+        <v>635.0998432705848</v>
       </c>
       <c r="X46" t="n">
-        <v>731.7606342947773</v>
+        <v>731.6806342947783</v>
       </c>
       <c r="Y46" t="n">
-        <v>731.7606342947773</v>
+        <v>788.6399349738106</v>
       </c>
     </row>
   </sheetData>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>300.4507139686307</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>321.8400703517588</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L2" t="n">
-        <v>309.2909949748744</v>
+        <v>234.1880104510425</v>
       </c>
       <c r="M2" t="n">
-        <v>846.2608914614127</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>128.5418702571336</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>235.7417089435049</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>846.2608914614127</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N5" t="n">
-        <v>778.0826666125488</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>128.5418702571336</v>
+        <v>362.2957550800353</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2405037325275146</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K8" t="n">
-        <v>183.3412755627362</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N8" t="n">
-        <v>778.0826666125488</v>
+        <v>584.9827562456367</v>
       </c>
       <c r="O8" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.5418702571336</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,28 +8675,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>470.5539648241206</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>427.8625025125627</v>
       </c>
       <c r="M11" t="n">
-        <v>299.3167457327696</v>
+        <v>947.3167457327725</v>
       </c>
       <c r="N11" t="n">
-        <v>877.3401037984784</v>
+        <v>401.7027692152149</v>
       </c>
       <c r="O11" t="n">
-        <v>50.76301021994976</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>423.7791327534228</v>
       </c>
       <c r="M14" t="n">
-        <v>948.3167457327697</v>
+        <v>947.3167457327697</v>
       </c>
       <c r="N14" t="n">
-        <v>872.7740959253404</v>
+        <v>876.3401037984784</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>423.7791327534228</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>948.3167457327697</v>
+        <v>947.3167457327697</v>
       </c>
       <c r="N17" t="n">
-        <v>872.7740959253404</v>
+        <v>876.3401037984784</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9389,16 +9389,16 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>425.7387287130186</v>
+        <v>423.7791327534228</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>948.3167457327697</v>
+        <v>947.3167457327697</v>
       </c>
       <c r="N20" t="n">
-        <v>877.3401037984784</v>
+        <v>876.3401037984784</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9623,19 +9623,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>423.7791327534328</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>948.3167457327697</v>
+        <v>947.3167457327743</v>
       </c>
       <c r="N23" t="n">
-        <v>872.7740959253404</v>
+        <v>876.3401037984829</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9863,19 +9863,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>471.5539648241206</v>
+        <v>470.5539648241293</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>948.3167457327697</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N26" t="n">
-        <v>401.2201311012197</v>
+        <v>564.050238431854</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>483.2102967097741</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -10100,16 +10100,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>471.5539648241206</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>427.8625025125715</v>
       </c>
       <c r="M29" t="n">
-        <v>948.3167457327697</v>
+        <v>349.5623940667381</v>
       </c>
       <c r="N29" t="n">
-        <v>237.8538857804642</v>
+        <v>876.3401037984834</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10334,19 +10334,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>471.5539648241206</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>428.8625025125627</v>
+        <v>47.80341426036421</v>
       </c>
       <c r="M32" t="n">
-        <v>948.3167457327697</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N32" t="n">
-        <v>402.6623651748134</v>
+        <v>876.3401037984806</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>22.18109136266131</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10577,13 +10577,13 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>253.2942842686508</v>
       </c>
       <c r="M35" t="n">
-        <v>861.3167457327697</v>
+        <v>860.3167457327716</v>
       </c>
       <c r="N35" t="n">
-        <v>790.3401037984784</v>
+        <v>789.3401037984802</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>277.4349715908314</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10665,7 +10665,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O36" t="n">
-        <v>382.6817988009037</v>
+        <v>380.4701772165901</v>
       </c>
       <c r="P36" t="n">
         <v>219.1507118405495</v>
@@ -10811,16 +10811,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>383.5539648241333</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>686.2658893747832</v>
+        <v>860.3167457327716</v>
       </c>
       <c r="N38" t="n">
-        <v>228.3401037984784</v>
+        <v>228.7756866568116</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>584.1810913626614</v>
+        <v>22.18109136266131</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10899,7 +10899,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N39" t="n">
-        <v>485.4085271713503</v>
+        <v>483.1969055870218</v>
       </c>
       <c r="O39" t="n">
         <v>382.6817988009037</v>
@@ -11048,16 +11048,16 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>383.5539648241335</v>
       </c>
       <c r="L41" t="n">
-        <v>341.8625025125629</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>774.708123448377</v>
+        <v>860.3167457327697</v>
       </c>
       <c r="N41" t="n">
-        <v>790.3401037984784</v>
+        <v>659.0804232429703</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11139,7 +11139,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O42" t="n">
-        <v>382.6817988009037</v>
+        <v>380.470177216568</v>
       </c>
       <c r="P42" t="n">
         <v>219.1507118405495</v>
@@ -11291,10 +11291,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>686.2658893747832</v>
+        <v>299.3167457327696</v>
       </c>
       <c r="N44" t="n">
-        <v>790.3401037984784</v>
+        <v>612.3296514809449</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>22.18109136266131</v>
+        <v>583.1810913626632</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11367,7 +11367,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>388.0893364597981</v>
+        <v>385.8777148754695</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.694822225952521e-13</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -23280,7 +23280,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.956056855791587</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -23511,7 +23511,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.956056855791758</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -23760,7 +23760,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.956056855791644</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.956056855791758</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24234,7 +24234,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.956056855772772</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2.956056855757652</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24663,7 +24663,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>2.956056855732257</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24939,7 +24939,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.956056855757652</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -25134,7 +25134,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7048568557918031</v>
+        <v>4.585656855727581</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -25374,7 +25374,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7048568557481687</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -25425,7 +25425,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>4.58565685574203</v>
       </c>
     </row>
     <row r="39">
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>4.585656855741945</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -25644,7 +25644,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.7048568557913342</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -25845,7 +25845,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>4.585656855741945</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -25881,7 +25881,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.7048568557917747</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>790769.1786342333</v>
+        <v>790659.3366342334</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1483426.55081716</v>
+        <v>1483316.70881716</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2176083.923000088</v>
+        <v>2175974.081000088</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2867832.671849682</v>
+        <v>2867608.70052902</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3560490.04403261</v>
+        <v>3560136.656542802</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4253147.416215537</v>
+        <v>4252664.612556582</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4945804.788398461</v>
+        <v>4945192.568570361</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5638462.160581386</v>
+        <v>5637720.52458414</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6331119.53276431</v>
+        <v>6330248.48059792</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7023776.904947234</v>
+        <v>7022776.436611701</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7716434.277130163</v>
+        <v>7715304.392625485</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8400834.492498131</v>
+        <v>8399506.574742904</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9093461.006047918</v>
+        <v>9091963.18686869</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9786087.519597704</v>
+        <v>9784419.79899448</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10478714.03314749</v>
+        <v>10476876.41112027</v>
       </c>
     </row>
   </sheetData>
@@ -26272,46 +26272,46 @@
         <v>1511252.448399114</v>
       </c>
       <c r="C2" t="n">
-        <v>1511252.448399114</v>
+        <v>1511252.448399113</v>
       </c>
       <c r="D2" t="n">
         <v>1511252.448399113</v>
       </c>
       <c r="E2" t="n">
-        <v>1511252.448399114</v>
+        <v>1510970.085848249</v>
       </c>
       <c r="F2" t="n">
-        <v>1511252.448399114</v>
+        <v>1510970.085848249</v>
       </c>
       <c r="G2" t="n">
-        <v>1511252.448399114</v>
+        <v>1510970.085848249</v>
       </c>
       <c r="H2" t="n">
-        <v>1511252.448399114</v>
+        <v>1510970.085848249</v>
       </c>
       <c r="I2" t="n">
-        <v>1511252.448399115</v>
+        <v>1510970.08584825</v>
       </c>
       <c r="J2" t="n">
-        <v>1511252.448399115</v>
+        <v>1510970.085848252</v>
       </c>
       <c r="K2" t="n">
-        <v>1511252.448399115</v>
+        <v>1510970.085848255</v>
       </c>
       <c r="L2" t="n">
-        <v>1511252.448399115</v>
+        <v>1510970.085848252</v>
       </c>
       <c r="M2" t="n">
-        <v>1511185.120472248</v>
+        <v>1510814.426456255</v>
       </c>
       <c r="N2" t="n">
-        <v>1511185.120472253</v>
+        <v>1510814.426456254</v>
       </c>
       <c r="O2" t="n">
-        <v>1511185.120472249</v>
+        <v>1510814.426456253</v>
       </c>
       <c r="P2" t="n">
-        <v>1511185.120472248</v>
+        <v>1510814.426456253</v>
       </c>
     </row>
     <row r="3">
@@ -26321,7 +26321,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231098</v>
+        <v>232073</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>592475</v>
+        <v>591148</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388448</v>
+        <v>388448.0000000031</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>85376</v>
+        <v>85024.00000000144</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101187</v>
+        <v>601967.7658514546</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.25402263</v>
+        <v>599959.4017938484</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.6066068059</v>
+        <v>597948.3132650448</v>
       </c>
       <c r="E4" t="n">
-        <v>514005.3727838712</v>
+        <v>513751.7523916513</v>
       </c>
       <c r="F4" t="n">
-        <v>512320.9448683569</v>
+        <v>512067.1546396873</v>
       </c>
       <c r="G4" t="n">
-        <v>510634.1925055168</v>
+        <v>510380.2322060293</v>
       </c>
       <c r="H4" t="n">
-        <v>508945.0990266501</v>
+        <v>508690.9684202963</v>
       </c>
       <c r="I4" t="n">
-        <v>507253.6475458712</v>
+        <v>506999.3463949003</v>
       </c>
       <c r="J4" t="n">
-        <v>505559.8209559915</v>
+        <v>505305.349020928</v>
       </c>
       <c r="K4" t="n">
-        <v>503863.6019243028</v>
+        <v>503608.9589639227</v>
       </c>
       <c r="L4" t="n">
-        <v>502164.9728882493</v>
+        <v>501910.1586595572</v>
       </c>
       <c r="M4" t="n">
-        <v>506566.2673210928</v>
+        <v>506308.9084534685</v>
       </c>
       <c r="N4" t="n">
-        <v>504800.3868513865</v>
+        <v>504542.813529751</v>
       </c>
       <c r="O4" t="n">
-        <v>503031.9520361847</v>
+        <v>502774.1639503342</v>
       </c>
       <c r="P4" t="n">
-        <v>501260.9436696268</v>
+        <v>501002.9405070193</v>
       </c>
     </row>
     <row r="5">
@@ -26425,49 +26425,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="C5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="D5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="E5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.149</v>
       </c>
       <c r="F5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.149</v>
       </c>
       <c r="G5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.149</v>
       </c>
       <c r="H5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.149</v>
       </c>
       <c r="I5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.149</v>
       </c>
       <c r="J5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.14900000053</v>
       </c>
       <c r="K5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.14900000053</v>
       </c>
       <c r="L5" t="n">
-        <v>74009.94899999999</v>
+        <v>73949.14900000053</v>
       </c>
       <c r="M5" t="n">
-        <v>70738.005</v>
+        <v>70677.20500000077</v>
       </c>
       <c r="N5" t="n">
-        <v>70738.005</v>
+        <v>70677.20500000077</v>
       </c>
       <c r="O5" t="n">
-        <v>70738.005</v>
+        <v>70677.20500000077</v>
       </c>
       <c r="P5" t="n">
-        <v>70738.005</v>
+        <v>70677.20500000077</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>619144.8721889952</v>
+        <v>618599.4825476592</v>
       </c>
       <c r="C6" t="n">
-        <v>852251.7943764837</v>
+        <v>852680.8466052652</v>
       </c>
       <c r="D6" t="n">
-        <v>854263.4417923075</v>
+        <v>854691.9351340682</v>
       </c>
       <c r="E6" t="n">
-        <v>330762.1266152428</v>
+        <v>332121.1844565978</v>
       </c>
       <c r="F6" t="n">
-        <v>924921.5545307572</v>
+        <v>924953.782208562</v>
       </c>
       <c r="G6" t="n">
-        <v>926608.3068935976</v>
+        <v>926640.7046422195</v>
       </c>
       <c r="H6" t="n">
-        <v>928297.4003724643</v>
+        <v>928329.9684279524</v>
       </c>
       <c r="I6" t="n">
-        <v>929988.8518532442</v>
+        <v>930021.5904533501</v>
       </c>
       <c r="J6" t="n">
-        <v>543234.6784431231</v>
+        <v>543267.5878273207</v>
       </c>
       <c r="K6" t="n">
-        <v>933378.8974748119</v>
+        <v>933411.9778843318</v>
       </c>
       <c r="L6" t="n">
-        <v>935077.5265108655</v>
+        <v>935110.7781886943</v>
       </c>
       <c r="M6" t="n">
-        <v>848504.8481511556</v>
+        <v>848804.3130027845</v>
       </c>
       <c r="N6" t="n">
-        <v>935646.7286208664</v>
+        <v>935594.4079265019</v>
       </c>
       <c r="O6" t="n">
-        <v>680615.1634360644</v>
+        <v>680563.0575059183</v>
       </c>
       <c r="P6" t="n">
-        <v>939186.1718026217</v>
+        <v>939134.2809492332</v>
       </c>
     </row>
   </sheetData>
@@ -26807,13 +26807,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
         <v>347</v>
@@ -26868,40 +26868,40 @@
         <v>374</v>
       </c>
       <c r="E4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="I4" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J4" t="n">
-        <v>649</v>
+        <v>648.0000000000088</v>
       </c>
       <c r="K4" t="n">
-        <v>649</v>
+        <v>648.0000000000088</v>
       </c>
       <c r="L4" t="n">
-        <v>649</v>
+        <v>648.0000000000088</v>
       </c>
       <c r="M4" t="n">
-        <v>562</v>
+        <v>561.0000000000128</v>
       </c>
       <c r="N4" t="n">
-        <v>562</v>
+        <v>561.0000000000128</v>
       </c>
       <c r="O4" t="n">
-        <v>562</v>
+        <v>561.0000000000128</v>
       </c>
       <c r="P4" t="n">
-        <v>562</v>
+        <v>561.0000000000128</v>
       </c>
     </row>
   </sheetData>
@@ -27008,7 +27008,7 @@
         <v>24</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27085,13 +27085,13 @@
         <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
@@ -27100,7 +27100,7 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>374.0000000000016</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27109,7 +27109,7 @@
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N4" t="n">
         <v>-0</v>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
-        <v>398.2013121321733</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27518,22 +27518,22 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>200.2217829794704</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27566,7 +27566,7 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>69.98968377575062</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27600,28 +27600,28 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>304.1318513503163</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
+        <v>244.858135136612</v>
+      </c>
+      <c r="H4" t="n">
         <v>400</v>
       </c>
-      <c r="H4" t="n">
-        <v>227.1357818393235</v>
-      </c>
       <c r="I4" t="n">
-        <v>266.2979670144121</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>22.26478490148153</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K4" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27654,13 +27654,13 @@
         <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27685,13 +27685,13 @@
         <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>398.0465935392086</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27749,10 +27749,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
@@ -27761,16 +27761,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>56.41623965604498</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27803,10 +27803,10 @@
         <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>30.47344446279683</v>
+        <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>107.9194317782221</v>
+        <v>400</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27831,16 +27831,16 @@
         <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
@@ -27849,16 +27849,16 @@
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>171.1020457840527</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J7" t="n">
-        <v>22.26478490148153</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K7" t="n">
-        <v>301.7053239698922</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L7" t="n">
-        <v>396.2015953708939</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>209.2386648669134</v>
+        <v>248.737551335911</v>
       </c>
       <c r="U7" t="n">
         <v>400</v>
       </c>
       <c r="V7" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W7" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X7" t="n">
+        <v>247.4436454301076</v>
+      </c>
+      <c r="Y7" t="n">
         <v>400</v>
-      </c>
-      <c r="W7" t="n">
-        <v>400</v>
-      </c>
-      <c r="X7" t="n">
-        <v>400</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27922,13 +27922,13 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>225.120779732817</v>
+        <v>222.9148456338345</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27986,7 +27986,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>153.0073197767764</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
@@ -27995,16 +27995,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0491815260438</v>
+        <v>72.35218209456139</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -28031,10 +28031,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28052,7 +28052,7 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>45.86273944538755</v>
+        <v>400</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28071,31 +28071,31 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>390.6571118022683</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>22.26478490148153</v>
+        <v>235.1415097211986</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.1680042930194</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T10" t="n">
-        <v>209.2386648669134</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28192,7 +28192,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>162.3267652318248</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S11" t="n">
         <v>321</v>
@@ -28229,16 +28229,16 @@
         <v>321</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>215.6455832169963</v>
       </c>
       <c r="E12" t="n">
-        <v>137.8407332208562</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>321</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>77.80484999613995</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>321</v>
@@ -28292,7 +28292,7 @@
         <v>321</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -28326,10 +28326,10 @@
         <v>321</v>
       </c>
       <c r="J13" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="K13" t="n">
-        <v>315.8198010595346</v>
+        <v>321</v>
       </c>
       <c r="L13" t="n">
         <v>321</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>162.3267652318248</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S14" t="n">
         <v>321</v>
@@ -28466,10 +28466,10 @@
         <v>321</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R15" t="n">
         <v>321</v>
@@ -28529,7 +28529,7 @@
         <v>321</v>
       </c>
       <c r="Y15" t="n">
-        <v>215.6455832169962</v>
+        <v>137.8407332208561</v>
       </c>
     </row>
     <row r="16">
@@ -28545,7 +28545,7 @@
         <v>321</v>
       </c>
       <c r="D16" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="E16" t="n">
         <v>321</v>
@@ -28602,7 +28602,7 @@
         <v>321</v>
       </c>
       <c r="W16" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
       <c r="X16" t="n">
         <v>321</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>162.3267652318248</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28700,7 +28700,7 @@
         <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>215.6455832169962</v>
+        <v>137.8407332208562</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -28742,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R18" t="n">
         <v>321</v>
@@ -28776,13 +28776,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
       <c r="C19" t="n">
         <v>321</v>
       </c>
       <c r="D19" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="E19" t="n">
         <v>321</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>162.3267652318248</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R21" t="n">
         <v>321</v>
@@ -28991,7 +28991,7 @@
         <v>321</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>137.8407332208563</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -29000,7 +29000,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>215.6455832169962</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>321</v>
@@ -29013,7 +29013,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>315.8198010595348</v>
+        <v>321</v>
       </c>
       <c r="C22" t="n">
         <v>321</v>
@@ -29022,7 +29022,7 @@
         <v>321</v>
       </c>
       <c r="E22" t="n">
-        <v>321</v>
+        <v>315.8198010595347</v>
       </c>
       <c r="F22" t="n">
         <v>321</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>162.3267652318248</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S23" t="n">
         <v>321</v>
@@ -29171,13 +29171,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>321</v>
+        <v>137.8407332208562</v>
       </c>
       <c r="C24" t="n">
-        <v>215.6455832169962</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R24" t="n">
         <v>321</v>
@@ -29274,10 +29274,10 @@
         <v>321</v>
       </c>
       <c r="J25" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="K25" t="n">
-        <v>321</v>
+        <v>315.8198010595346</v>
       </c>
       <c r="L25" t="n">
         <v>321</v>
@@ -29350,7 +29350,7 @@
         <v>321</v>
       </c>
       <c r="I26" t="n">
-        <v>95.37664769425496</v>
+        <v>96.3013908384635</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>163.2515083760331</v>
+        <v>163.2515083760552</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29411,16 +29411,16 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>321</v>
+        <v>137.8407332208567</v>
       </c>
       <c r="E27" t="n">
         <v>321</v>
       </c>
       <c r="F27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>321</v>
@@ -29471,13 +29471,13 @@
         <v>321</v>
       </c>
       <c r="W27" t="n">
-        <v>137.8407332208563</v>
+        <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28">
@@ -29499,7 +29499,7 @@
         <v>321</v>
       </c>
       <c r="F28" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="G28" t="n">
         <v>321</v>
@@ -29544,7 +29544,7 @@
         <v>321</v>
       </c>
       <c r="U28" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
       <c r="V28" t="n">
         <v>321</v>
@@ -29587,7 +29587,7 @@
         <v>321</v>
       </c>
       <c r="I29" t="n">
-        <v>95.37664769425513</v>
+        <v>96.3013908384635</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>163.2515083760331</v>
+        <v>163.2515083760584</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29645,19 +29645,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C30" t="n">
-        <v>321</v>
+        <v>137.8407332208567</v>
       </c>
       <c r="D30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>215.6455832169961</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R30" t="n">
         <v>321</v>
@@ -29711,7 +29711,7 @@
         <v>321</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y30" t="n">
         <v>321</v>
@@ -29781,7 +29781,7 @@
         <v>321</v>
       </c>
       <c r="U31" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="V31" t="n">
         <v>321</v>
@@ -29793,7 +29793,7 @@
         <v>321</v>
       </c>
       <c r="Y31" t="n">
-        <v>321</v>
+        <v>315.8198010595348</v>
       </c>
     </row>
     <row r="32">
@@ -29821,7 +29821,7 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>320.0752568557916</v>
+        <v>321</v>
       </c>
       <c r="I32" t="n">
         <v>96.3013908384635</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>163.2515083760331</v>
+        <v>163.2515083760552</v>
       </c>
       <c r="S32" t="n">
         <v>321</v>
@@ -29885,7 +29885,7 @@
         <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>215.6455832169962</v>
+        <v>137.8407332208567</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>77.80484999613995</v>
       </c>
       <c r="R33" t="n">
         <v>321</v>
@@ -29976,7 +29976,7 @@
         <v>321</v>
       </c>
       <c r="G34" t="n">
-        <v>315.8198010595347</v>
+        <v>321</v>
       </c>
       <c r="H34" t="n">
         <v>321</v>
@@ -29985,7 +29985,7 @@
         <v>321</v>
       </c>
       <c r="J34" t="n">
-        <v>321</v>
+        <v>315.8198010595349</v>
       </c>
       <c r="K34" t="n">
         <v>321</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>163.2515083760331</v>
+        <v>163.2515083760187</v>
       </c>
       <c r="S35" t="n">
         <v>345</v>
@@ -30122,16 +30122,16 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="D36" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>324.9931585165368</v>
@@ -30140,7 +30140,7 @@
         <v>324.959653224157</v>
       </c>
       <c r="I36" t="n">
-        <v>110.6804235242006</v>
+        <v>107.4842761768635</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30185,7 +30185,7 @@
         <v>345</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="Y36" t="n">
         <v>345</v>
@@ -30210,25 +30210,25 @@
         <v>345</v>
       </c>
       <c r="F37" t="n">
-        <v>324.4245318412749</v>
+        <v>345</v>
       </c>
       <c r="G37" t="n">
         <v>244.418135136612</v>
       </c>
       <c r="H37" t="n">
-        <v>345</v>
+        <v>223.2077490524383</v>
       </c>
       <c r="I37" t="n">
         <v>345</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>126.2506660784599</v>
       </c>
       <c r="K37" t="n">
-        <v>345</v>
+        <v>215.821429538848</v>
       </c>
       <c r="L37" t="n">
-        <v>345</v>
+        <v>330.5174970102382</v>
       </c>
       <c r="M37" t="n">
         <v>345</v>
@@ -30261,7 +30261,7 @@
         <v>345</v>
       </c>
       <c r="W37" t="n">
-        <v>226.3728098387097</v>
+        <v>345</v>
       </c>
       <c r="X37" t="n">
         <v>345</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>163.2515083760777</v>
+        <v>163.2515083760331</v>
       </c>
       <c r="S38" t="n">
         <v>345</v>
@@ -30359,7 +30359,7 @@
         <v>345</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -30368,16 +30368,16 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>324.9931585165368</v>
       </c>
       <c r="H39" t="n">
-        <v>324.959653224157</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>183.121515858217</v>
+        <v>170.6125370592976</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30407,7 +30407,7 @@
         <v>345</v>
       </c>
       <c r="S39" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>345</v>
@@ -30441,19 +30441,19 @@
         <v>345</v>
       </c>
       <c r="D40" t="n">
-        <v>345</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E40" t="n">
         <v>345</v>
       </c>
       <c r="F40" t="n">
-        <v>345.0000000000002</v>
+        <v>345</v>
       </c>
       <c r="G40" t="n">
         <v>345</v>
       </c>
       <c r="H40" t="n">
-        <v>223.8426669778866</v>
+        <v>345</v>
       </c>
       <c r="I40" t="n">
         <v>345</v>
@@ -30489,16 +30489,16 @@
         <v>345</v>
       </c>
       <c r="T40" t="n">
-        <v>345</v>
+        <v>310.5089485448249</v>
       </c>
       <c r="U40" t="n">
         <v>345</v>
       </c>
       <c r="V40" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W40" t="n">
         <v>345</v>
-      </c>
-      <c r="W40" t="n">
-        <v>226.3728098387097</v>
       </c>
       <c r="X40" t="n">
         <v>345</v>
@@ -30599,13 +30599,13 @@
         <v>345</v>
       </c>
       <c r="D42" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>324.9931585165368</v>
@@ -30614,7 +30614,7 @@
         <v>324.959653224157</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>185.2891261730247</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30647,22 +30647,22 @@
         <v>345</v>
       </c>
       <c r="T42" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>345</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="Y42" t="n">
-        <v>190.8131762984275</v>
+        <v>345</v>
       </c>
     </row>
     <row r="43">
@@ -30672,22 +30672,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>287.1138003370787</v>
+        <v>345</v>
       </c>
       <c r="C43" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D43" t="n">
-        <v>285.5362180555555</v>
+        <v>345</v>
       </c>
       <c r="E43" t="n">
-        <v>280.9809048369565</v>
+        <v>345</v>
       </c>
       <c r="F43" t="n">
-        <v>274.3828559677419</v>
+        <v>315.1392702196712</v>
       </c>
       <c r="G43" t="n">
-        <v>285.6721715726704</v>
+        <v>345</v>
       </c>
       <c r="H43" t="n">
         <v>345</v>
@@ -30696,13 +30696,13 @@
         <v>345</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>345</v>
       </c>
-      <c r="K43" t="n">
-        <v>215.821429538848</v>
-      </c>
       <c r="L43" t="n">
-        <v>330.5174970102382</v>
+        <v>345</v>
       </c>
       <c r="M43" t="n">
         <v>345</v>
@@ -30726,7 +30726,7 @@
         <v>345</v>
       </c>
       <c r="T43" t="n">
-        <v>345</v>
+        <v>207.3509599488807</v>
       </c>
       <c r="U43" t="n">
         <v>345</v>
@@ -30741,7 +30741,7 @@
         <v>345</v>
       </c>
       <c r="Y43" t="n">
-        <v>287.4653528494624</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44">
@@ -30836,22 +30836,22 @@
         <v>345</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>324.9931585165368</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>324.959653224157</v>
       </c>
       <c r="I45" t="n">
-        <v>191.4287443819146</v>
+        <v>95.16909513362521</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30893,10 +30893,10 @@
         <v>345</v>
       </c>
       <c r="W45" t="n">
-        <v>258.8879214801631</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -30912,7 +30912,7 @@
         <v>345</v>
       </c>
       <c r="C46" t="n">
-        <v>272.7252466480447</v>
+        <v>345</v>
       </c>
       <c r="D46" t="n">
         <v>345</v>
@@ -30930,16 +30930,16 @@
         <v>345</v>
       </c>
       <c r="I46" t="n">
-        <v>345</v>
+        <v>248.8765502675103</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>235.0248773190894</v>
+        <v>215.821429538848</v>
       </c>
       <c r="L46" t="n">
-        <v>345</v>
+        <v>330.5174970102382</v>
       </c>
       <c r="M46" t="n">
         <v>345</v>
@@ -30978,7 +30978,7 @@
         <v>345</v>
       </c>
       <c r="Y46" t="n">
-        <v>287.4653528494624</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H2" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I2" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J2" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M2" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N2" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O2" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P2" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R2" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S2" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T2" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I3" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K3" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L3" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M3" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O3" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P3" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R3" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S3" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I4" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J4" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K4" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L4" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M4" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N4" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O4" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P4" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R4" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S4" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H5" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I5" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J5" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K5" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M5" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N5" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O5" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P5" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R5" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S5" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T5" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H6" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I6" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J6" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K6" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L6" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M6" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O6" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P6" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R6" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S6" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H7" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I7" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J7" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K7" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L7" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M7" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N7" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O7" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P7" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R7" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S7" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H8" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I8" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J8" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M8" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N8" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O8" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P8" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R8" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S8" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T8" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H9" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I9" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J9" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K9" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L9" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M9" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O9" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P9" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R9" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S9" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H10" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I10" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J10" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K10" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L10" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M10" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N10" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O10" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P10" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R10" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S10" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T10" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34743,13 +34743,13 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>300.2102102361031</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K2" t="n">
         <v>374</v>
       </c>
       <c r="L2" t="n">
-        <v>374</v>
+        <v>299.5314174862184</v>
       </c>
       <c r="M2" t="n">
         <v>374</v>
@@ -34761,10 +34761,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K3" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M3" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O3" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P3" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34886,28 +34886,28 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>23.1509465133598</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I4" t="n">
-        <v>95.19592123035935</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.83199570698065</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T4" t="n">
-        <v>190.7613351330866</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0516415124273</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,13 +34980,13 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>235.5012052109774</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K5" t="n">
         <v>374</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517591</v>
       </c>
       <c r="M5" t="n">
         <v>374</v>
@@ -34998,10 +34998,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>234.1880104510424</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K6" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L6" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M6" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O6" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P6" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35117,22 +35117,22 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>155.1400615846995</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H7" t="n">
-        <v>172.8642181606765</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -35141,7 +35141,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>34.55438623432293</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>39.50659138703032</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0516415124273</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35217,25 +35217,25 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>235.5012052109774</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517586</v>
       </c>
       <c r="M8" t="n">
         <v>374</v>
       </c>
       <c r="N8" t="n">
-        <v>374</v>
+        <v>181.6174062160025</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
         <v>374</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K9" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L9" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M9" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O9" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P9" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35357,31 +35357,31 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>105.1208937467128</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>213.0042166229958</v>
       </c>
       <c r="K10" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35408,19 +35408,19 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,28 +35454,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K11" t="n">
-        <v>177.4460351758794</v>
+        <v>648</v>
       </c>
       <c r="L11" t="n">
-        <v>220.1374974874373</v>
+        <v>648</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>648.0000000000028</v>
       </c>
       <c r="N11" t="n">
-        <v>649</v>
+        <v>173.3626654167364</v>
       </c>
       <c r="O11" t="n">
-        <v>215.5527135101789</v>
+        <v>164.7897032902292</v>
       </c>
       <c r="P11" t="n">
         <v>200.3120706125849</v>
       </c>
       <c r="Q11" t="n">
-        <v>593.6709819069124</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35612,10 +35612,10 @@
         <v>163.184183724144</v>
       </c>
       <c r="J13" t="n">
-        <v>329.9707069017971</v>
+        <v>324.7905079613318</v>
       </c>
       <c r="K13" t="n">
-        <v>99.99837152068662</v>
+        <v>105.178570461152</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K14" t="n">
         <v>177.4460351758794</v>
       </c>
       <c r="L14" t="n">
-        <v>220.1374974874373</v>
+        <v>643.9166302408599</v>
       </c>
       <c r="M14" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="N14" t="n">
-        <v>644.4339921268619</v>
+        <v>648</v>
       </c>
       <c r="O14" t="n">
         <v>164.7897032902292</v>
@@ -35831,7 +35831,7 @@
         <v>48.27475335195533</v>
       </c>
       <c r="D16" t="n">
-        <v>30.28358300397924</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E16" t="n">
         <v>40.01909516304346</v>
@@ -35888,7 +35888,7 @@
         <v>121.8296897837838</v>
       </c>
       <c r="W16" t="n">
-        <v>94.62719016129032</v>
+        <v>89.44699122082511</v>
       </c>
       <c r="X16" t="n">
         <v>73.55635456989245</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K17" t="n">
-        <v>177.4460351758794</v>
+        <v>601.2251679293022</v>
       </c>
       <c r="L17" t="n">
-        <v>220.1374974874373</v>
+        <v>220.1374974874371</v>
       </c>
       <c r="M17" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="N17" t="n">
-        <v>644.4339921268619</v>
+        <v>648</v>
       </c>
       <c r="O17" t="n">
         <v>164.7897032902292</v>
@@ -36062,13 +36062,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33.88619966292134</v>
+        <v>28.7060007224561</v>
       </c>
       <c r="C19" t="n">
         <v>48.27475335195533</v>
       </c>
       <c r="D19" t="n">
-        <v>30.28358300397924</v>
+        <v>35.46378194444452</v>
       </c>
       <c r="E19" t="n">
         <v>40.01909516304346</v>
@@ -36168,16 +36168,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K20" t="n">
-        <v>603.184763888898</v>
+        <v>601.2251679293022</v>
       </c>
       <c r="L20" t="n">
-        <v>220.1374974874373</v>
+        <v>220.1374974874371</v>
       </c>
       <c r="M20" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="N20" t="n">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="O20" t="n">
         <v>164.7897032902292</v>
@@ -36299,7 +36299,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28.7060007224561</v>
+        <v>33.88619966292134</v>
       </c>
       <c r="C22" t="n">
         <v>48.27475335195533</v>
@@ -36308,7 +36308,7 @@
         <v>35.46378194444452</v>
       </c>
       <c r="E22" t="n">
-        <v>40.01909516304346</v>
+        <v>34.83889622257817</v>
       </c>
       <c r="F22" t="n">
         <v>46.61714403225807</v>
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>513.658479084785</v>
+        <v>83.35374249862829</v>
       </c>
       <c r="K23" t="n">
-        <v>177.4460351758794</v>
+        <v>601.2251679293122</v>
       </c>
       <c r="L23" t="n">
-        <v>220.1374974874373</v>
+        <v>220.1374974874371</v>
       </c>
       <c r="M23" t="n">
-        <v>649</v>
+        <v>648.0000000000047</v>
       </c>
       <c r="N23" t="n">
-        <v>644.4339921268619</v>
+        <v>648.0000000000047</v>
       </c>
       <c r="O23" t="n">
         <v>164.7897032902292</v>
@@ -36560,10 +36560,10 @@
         <v>163.184183724144</v>
       </c>
       <c r="J25" t="n">
-        <v>324.7905079613318</v>
+        <v>329.9707069017971</v>
       </c>
       <c r="K25" t="n">
-        <v>105.178570461152</v>
+        <v>99.99837152068662</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -36642,19 +36642,19 @@
         <v>513.658479084785</v>
       </c>
       <c r="K26" t="n">
-        <v>649</v>
+        <v>648.0000000000086</v>
       </c>
       <c r="L26" t="n">
         <v>220.1374974874373</v>
       </c>
       <c r="M26" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>172.8800273027414</v>
+        <v>335.7101346333756</v>
       </c>
       <c r="O26" t="n">
-        <v>164.7897032902292</v>
+        <v>648.0000000000033</v>
       </c>
       <c r="P26" t="n">
         <v>200.3120706125849</v>
@@ -36663,7 +36663,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.204835640661644e-11</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -36785,7 +36785,7 @@
         <v>40.01909516304346</v>
       </c>
       <c r="F28" t="n">
-        <v>41.43694509179277</v>
+        <v>46.61714403225807</v>
       </c>
       <c r="G28" t="n">
         <v>76.58186486338801</v>
@@ -36830,7 +36830,7 @@
         <v>113.6490400511193</v>
       </c>
       <c r="U28" t="n">
-        <v>170.0757398730831</v>
+        <v>164.8955409326178</v>
       </c>
       <c r="V28" t="n">
         <v>121.8296897837838</v>
@@ -36879,16 +36879,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K29" t="n">
-        <v>649</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L29" t="n">
-        <v>220.1374974874373</v>
+        <v>648.0000000000088</v>
       </c>
       <c r="M29" t="n">
-        <v>649</v>
+        <v>50.2456483339685</v>
       </c>
       <c r="N29" t="n">
-        <v>9.513781981985804</v>
+        <v>648.0000000000051</v>
       </c>
       <c r="O29" t="n">
         <v>164.7897032902292</v>
@@ -37067,7 +37067,7 @@
         <v>113.6490400511193</v>
       </c>
       <c r="U31" t="n">
-        <v>164.8955409326178</v>
+        <v>170.0757398730831</v>
       </c>
       <c r="V31" t="n">
         <v>121.8296897837838</v>
@@ -37079,7 +37079,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y31" t="n">
-        <v>33.53464715053764</v>
+        <v>28.35444821007238</v>
       </c>
     </row>
     <row r="32">
@@ -37113,19 +37113,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>83.35374249862829</v>
+        <v>513.658479084785</v>
       </c>
       <c r="K32" t="n">
-        <v>649</v>
+        <v>177.4460351758794</v>
       </c>
       <c r="L32" t="n">
-        <v>649</v>
+        <v>267.9409117478014</v>
       </c>
       <c r="M32" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>174.322261376335</v>
+        <v>648.0000000000024</v>
       </c>
       <c r="O32" t="n">
         <v>164.7897032902292</v>
@@ -37134,10 +37134,10 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>593.6709819069124</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.204835640661644e-11</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -37262,7 +37262,7 @@
         <v>46.61714403225807</v>
       </c>
       <c r="G34" t="n">
-        <v>71.40166592292275</v>
+        <v>76.58186486338801</v>
       </c>
       <c r="H34" t="n">
         <v>97.79225094756171</v>
@@ -37271,7 +37271,7 @@
         <v>163.184183724144</v>
       </c>
       <c r="J34" t="n">
-        <v>329.9707069017971</v>
+        <v>324.790507961332</v>
       </c>
       <c r="K34" t="n">
         <v>105.178570461152</v>
@@ -37356,13 +37356,13 @@
         <v>177.4460351758794</v>
       </c>
       <c r="L35" t="n">
-        <v>220.1374974874372</v>
+        <v>473.4317817560881</v>
       </c>
       <c r="M35" t="n">
-        <v>562.0000000000001</v>
+        <v>561.0000000000019</v>
       </c>
       <c r="N35" t="n">
-        <v>562.0000000000001</v>
+        <v>561.0000000000019</v>
       </c>
       <c r="O35" t="n">
         <v>164.7897032902292</v>
@@ -37371,7 +37371,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q35" t="n">
-        <v>255.2538802281701</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37444,7 +37444,7 @@
         <v>328.7468614294096</v>
       </c>
       <c r="O36" t="n">
-        <v>419.0391822801049</v>
+        <v>416.8275606957912</v>
       </c>
       <c r="P36" t="n">
         <v>256.1913441372947</v>
@@ -37496,25 +37496,25 @@
         <v>64.01909516304346</v>
       </c>
       <c r="F37" t="n">
-        <v>50.04167587353297</v>
+        <v>70.61714403225807</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>121.7922509475617</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>187.184183724144</v>
       </c>
       <c r="J37" t="n">
-        <v>8.970706901797143</v>
+        <v>135.221372980257</v>
       </c>
       <c r="K37" t="n">
-        <v>129.178570461152</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>14.48250298976183</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37547,7 +37547,7 @@
         <v>145.8296897837838</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>118.6271901612903</v>
       </c>
       <c r="X37" t="n">
         <v>97.55635456989245</v>
@@ -37590,16 +37590,16 @@
         <v>513.658479084785</v>
       </c>
       <c r="K38" t="n">
-        <v>177.4460351758794</v>
+        <v>561.0000000000127</v>
       </c>
       <c r="L38" t="n">
         <v>220.1374974874373</v>
       </c>
       <c r="M38" t="n">
-        <v>386.9491436420136</v>
+        <v>561.0000000000019</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>0.4355828583331661</v>
       </c>
       <c r="O38" t="n">
         <v>164.7897032902292</v>
@@ -37608,10 +37608,10 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q38" t="n">
-        <v>562.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.455605357170406e-11</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -37678,7 +37678,7 @@
         <v>276.0650421645042</v>
       </c>
       <c r="N39" t="n">
-        <v>328.7468614294096</v>
+        <v>326.5352398450811</v>
       </c>
       <c r="O39" t="n">
         <v>419.0391822801049</v>
@@ -37727,19 +37727,19 @@
         <v>72.27475335195533</v>
       </c>
       <c r="D40" t="n">
-        <v>59.46378194444452</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>64.01909516304346</v>
       </c>
       <c r="F40" t="n">
-        <v>70.61714403225825</v>
+        <v>70.61714403225807</v>
       </c>
       <c r="G40" t="n">
         <v>100.581864863388</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6349179254483615</v>
+        <v>121.7922509475617</v>
       </c>
       <c r="I40" t="n">
         <v>187.184183724144</v>
@@ -37775,16 +37775,16 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>137.6490400511193</v>
+        <v>103.1579885959442</v>
       </c>
       <c r="U40" t="n">
         <v>194.0757398730831</v>
       </c>
       <c r="V40" t="n">
-        <v>145.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>118.6271901612903</v>
       </c>
       <c r="X40" t="n">
         <v>97.55635456989245</v>
@@ -37827,16 +37827,16 @@
         <v>83.35374249862829</v>
       </c>
       <c r="K41" t="n">
-        <v>177.4460351758794</v>
+        <v>561.000000000013</v>
       </c>
       <c r="L41" t="n">
-        <v>562</v>
+        <v>220.1374974874373</v>
       </c>
       <c r="M41" t="n">
-        <v>475.3913777156074</v>
+        <v>561.0000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>562.0000000000001</v>
+        <v>430.7403194444918</v>
       </c>
       <c r="O41" t="n">
         <v>164.7897032902292</v>
@@ -37918,7 +37918,7 @@
         <v>328.7468614294096</v>
       </c>
       <c r="O42" t="n">
-        <v>419.0391822801049</v>
+        <v>416.8275606957691</v>
       </c>
       <c r="P42" t="n">
         <v>256.1913441372947</v>
@@ -37958,22 +37958,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>57.88619966292134</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>59.46378194444452</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>64.01909516304346</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>40.75641425192931</v>
       </c>
       <c r="G43" t="n">
-        <v>41.25403643605845</v>
+        <v>100.581864863388</v>
       </c>
       <c r="H43" t="n">
         <v>121.7922509475617</v>
@@ -37982,13 +37982,13 @@
         <v>187.184183724144</v>
       </c>
       <c r="J43" t="n">
-        <v>353.9707069017971</v>
+        <v>8.970706901797143</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>129.178570461152</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>14.48250298976181</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>137.6490400511193</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>194.0757398730831</v>
@@ -38027,7 +38027,7 @@
         <v>97.55635456989245</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>57.53464715053764</v>
       </c>
     </row>
     <row r="44">
@@ -38070,10 +38070,10 @@
         <v>220.1374974874373</v>
       </c>
       <c r="M44" t="n">
-        <v>386.9491436420136</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>562.0000000000001</v>
+        <v>383.9895476824665</v>
       </c>
       <c r="O44" t="n">
         <v>164.7897032902292</v>
@@ -38082,7 +38082,7 @@
         <v>200.3120706125849</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>561.0000000000019</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38146,7 +38146,7 @@
         <v>311.6274301124894</v>
       </c>
       <c r="L45" t="n">
-        <v>436.150196103404</v>
+        <v>433.9385745190754</v>
       </c>
       <c r="M45" t="n">
         <v>276.0650421645042</v>
@@ -38198,7 +38198,7 @@
         <v>57.88619966292134</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>72.27475335195533</v>
       </c>
       <c r="D46" t="n">
         <v>59.46378194444452</v>
@@ -38216,16 +38216,16 @@
         <v>121.7922509475617</v>
       </c>
       <c r="I46" t="n">
-        <v>187.184183724144</v>
+        <v>91.0607339916543</v>
       </c>
       <c r="J46" t="n">
         <v>8.970706901797143</v>
       </c>
       <c r="K46" t="n">
-        <v>19.20344778024141</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>14.48250298976183</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -38264,7 +38264,7 @@
         <v>97.55635456989245</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>57.53464715053764</v>
       </c>
     </row>
   </sheetData>
